--- a/CardiauFflachCemeg.xlsx
+++ b/CardiauFflachCemeg.xlsx
@@ -1,23 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60D8CBA1-362C-4D78-B377-59E1AA6EBA0D}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD624D91-E9C6-4920-9A5F-E01A64C80668}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="5.1 Cemeg uned 1" sheetId="1" r:id="rId1"/>
     <sheet name="5.2 Cemeg uned 2" sheetId="3" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -34,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="59">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -42,109 +45,129 @@
     <t>Ateb</t>
   </si>
   <si>
+    <t>Delwedd Cwestiwn</t>
+  </si>
+  <si>
+    <t>Delwedd Ateb</t>
+  </si>
+  <si>
+    <t>Beth yw'r math o fondiau sydd rhwng metel ac anfetel?</t>
+  </si>
+  <si>
+    <t>Ionig</t>
+  </si>
+  <si>
+    <t>Beth yw'r math o fondiau sydd rhwng anfetel ac anfetel?</t>
+  </si>
+  <si>
+    <t>Cofalent</t>
+  </si>
+  <si>
+    <t>ê</t>
+  </si>
+  <si>
+    <t>Beth yw'r math o fondiau sydd mewn metelau?</t>
+  </si>
+  <si>
+    <t>Metelig</t>
+  </si>
+  <si>
+    <t>ô</t>
+  </si>
+  <si>
+    <t>Disgrifiwch neu gwnewch ddiagram sy'n dangos sut mae electronau yn trosglwyddo pan fydd atom sodiwm (Na 2.8.1) a clorin (Cl 2.8.7) yn bondio.</t>
+  </si>
+  <si>
+    <t>Mae'r electron o blisgyn allanol y sodiwm yn cael ei golli i blisgyn allanol y clorin.</t>
+  </si>
+  <si>
+    <t>Bondio_NaCl</t>
+  </si>
+  <si>
+    <t>Gwnewch ddiagram o'r ionau sodiwm a clorin sy'n ffurfio pan fydd atom sodiwm (Na 2.8.1) a clorin (Cl 2.8.7) yn bondio.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Ionau_Na_a_Cl</t>
+  </si>
+  <si>
+    <t>Beth yw adeiledd electronig yr ionau sodiwm a clorin sy'n ffurfio pan fydd atom sodiwm (Na 2.8.1) a clorin (Cl 2.8.7) yn bondio?</t>
+  </si>
+  <si>
+    <t>$Na^+$    2.8          $Cl^-$    2.8.8</t>
+  </si>
+  <si>
+    <t>Pam fod atomau yn bondio?</t>
+  </si>
+  <si>
+    <t>Er mwyn cael plisgyn allanol llawn o electronau</t>
+  </si>
+  <si>
+    <t>Pa fath o fondio sy'n digwydd pan fydd electronau yn cael eu rhannu rhwng 2 atom?</t>
+  </si>
+  <si>
+    <t>Pa fath o fondio sy'n digwydd pan fydd ionau positif yn cael eu dal efo'i gilydd gan y Môr o Electronau rhydd?</t>
+  </si>
+  <si>
+    <t>Beth yw'r adeiledd yma?</t>
+  </si>
+  <si>
+    <t>Ionig Enfawr</t>
+  </si>
+  <si>
+    <t>Adeiledd_ionig</t>
+  </si>
+  <si>
+    <t>Diemwnt</t>
+  </si>
+  <si>
+    <t>Adeiledd_Diemwnt</t>
+  </si>
+  <si>
+    <t>Graffit</t>
+  </si>
+  <si>
+    <t>Adeiledd_graffit</t>
+  </si>
+  <si>
+    <t>Buckminster Ffwleren</t>
+  </si>
+  <si>
+    <t>Adeiledd_Buckminsterffwleren</t>
+  </si>
+  <si>
+    <t>Moleciwlaidd Syml</t>
+  </si>
+  <si>
+    <t>Adeiledd_moleciwlaidd_syml</t>
+  </si>
+  <si>
+    <t>Nanotiwb carbon</t>
+  </si>
+  <si>
+    <t>Adeiledd_nanotiwb_carbon</t>
+  </si>
+  <si>
+    <t>Graffen</t>
+  </si>
+  <si>
+    <t>Adeiledd_graffen</t>
+  </si>
+  <si>
     <t>Delwedd</t>
   </si>
   <si>
-    <t>Beth yw uned pellter? 
-What is the unit for distance?</t>
-  </si>
-  <si>
-    <t>m</t>
-  </si>
-  <si>
-    <t>Beth yw uned buanedd? 
-What is the unit for speed?</t>
-  </si>
-  <si>
-    <t>m/s</t>
-  </si>
-  <si>
-    <t>Beth yw uned amser? 
-What is the unit for time?</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
-  <si>
-    <t>Beth yw uned cyflymiad? 
-What is the unit for acceleration?</t>
-  </si>
-  <si>
-    <t>Disgrifiwch mudiant y bws yn rhan A</t>
-  </si>
-  <si>
-    <t>Cyflymiad cyson</t>
-  </si>
-  <si>
-    <t>Disgrifiwch mudiant y bws yn rhan B</t>
-  </si>
-  <si>
-    <t>Disgrifiwch mudiant y bws yn rhan C</t>
-  </si>
-  <si>
-    <t>Disgrifiwch mudiant y bws yn rhan D</t>
-  </si>
-  <si>
-    <t>Cyflymder cyson (neu buanedd cyson)</t>
-  </si>
-  <si>
-    <t>Arafiad cyson</t>
-  </si>
-  <si>
-    <t>$m/s^2$</t>
-  </si>
-  <si>
-    <t>Beth yw pellter meddwl?</t>
-  </si>
-  <si>
-    <t>Beth yw pellter brecio?</t>
-  </si>
-  <si>
-    <t>ê</t>
-  </si>
-  <si>
-    <t>Y pellter mae'r cerbyd yn deithio cyn i'r gyrrwr bwyso'r brêc.</t>
-  </si>
-  <si>
-    <t>ô</t>
-  </si>
-  <si>
-    <t>Y pellter mae'r cerbyd yn deithio ar ôl i'r gyrrwr bwyso'r brêc.</t>
-  </si>
-  <si>
-    <t>Beth yw pellter stopio?</t>
-  </si>
-  <si>
-    <t>pellter stopio = pellter meddwl + pellter brecio</t>
-  </si>
-  <si>
-    <t>Sut mae cywasgran (crumple zone) yn helpu i amddiffyn teithwyr yn ystod gwrthdrawiad?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mae'n cynyddu'r amser mae'n gymryd i stopio - arafiad ar y teithwyr yn llai - grym ar y teithwyr yn llai - llai tebygol o gael anaf drwg. </t>
-  </si>
-  <si>
     <t>Beth sy'n fesur o inertia gwrthrych?</t>
   </si>
   <si>
+    <t>Màs y gwrthrych.</t>
+  </si>
+  <si>
     <t>à</t>
   </si>
   <si>
-    <t>Màs y gwrthrych.</t>
-  </si>
-  <si>
-    <t>Pa ffactorau sy'n cynyddu pellter meddwl?</t>
-  </si>
-  <si>
-    <t>Pa ffactorau sy'n cynyddu pellter brecio?</t>
-  </si>
-  <si>
-    <t>1) Cynyddu buanedd, 2) Lôn wlyb/rhewllyd, 3) teiars/breciau wedi treulio, 4) cynyddu màs y cerbyd</t>
-  </si>
-  <si>
-    <t>1) Cynyddu buanedd, 2) yfed alcohol/cyffuriau, 3) blinder, 4) Oedran hyn, 5) defnyddio ffon symudol</t>
-  </si>
-  <si>
     <t>Beth yw ystyr buanedd terfynol?</t>
   </si>
   <si>
@@ -154,6 +177,9 @@
     <t>Nodwch deddf gyntaf mudiant Newton.</t>
   </si>
   <si>
+    <t>Bydd gwrthrych yn parhau’n ddisymud (at rest), neu’n symud ar gyflymder cyson, os yw’r grymoedd arno yn gytbwys.</t>
+  </si>
+  <si>
     <t>Nodwch ail ddeddf  mudiant Newton.</t>
   </si>
   <si>
@@ -166,41 +192,35 @@
     <t>Os yw corff A yn rhoi grym ar corff B, yna bydd corff B yn rhoi grym hafal a dirgroes ar corff A.</t>
   </si>
   <si>
-    <t>Bydd gwrthrych yn parhau’n ddisymud (at rest), neu’n symud ar gyflymder cyson, os yw’r grymoedd arno yn gytbwys.</t>
+    <t>Enwch y ddau rym sydd yn gweithredu ar wrthrych sydd yn syrthio drwy'r aer?</t>
+  </si>
+  <si>
+    <t>Disgyrchiant (neu pwysau) a gwrthiant aer.</t>
+  </si>
+  <si>
+    <t>Mae plymiwr awyr yn neidio allan o awyren, beth sy'n digwydd i'r gwrthiant aer arno fel mae'n syrthio?</t>
   </si>
   <si>
     <t>Cynyddu</t>
   </si>
   <si>
-    <t>Enwch y ddau rym sydd yn gweithredu ar wrthrych sydd yn syrthio drwy'r aer?</t>
-  </si>
-  <si>
-    <t>Mae plymiwr awyr yn neidio allan o awyren, beth sy'n digwydd i'r gwrthiant aer arno fel mae'n syrthio?</t>
-  </si>
-  <si>
     <t>Mae plymiwr awyr yn neidio allan o awyren, beth sy'n digwydd i'w bwysau fel mae'n syrthio?</t>
   </si>
   <si>
     <t>Aros yn gyson</t>
   </si>
   <si>
-    <t>Disgyrchiant (neu pwysau) a gwrthiant aer.</t>
-  </si>
-  <si>
     <t>Disgrifiwch fudiant plymiwr awyr os yw'r gwrthiant aer arno yn  hafal i'w bwysau (grym disgyrchaint)?</t>
   </si>
   <si>
     <t>Buaned cyson neu cyflymder cyson (buanedd terfynol)</t>
-  </si>
-  <si>
-    <t>mudiant_gwrthrych.png</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -214,20 +234,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
@@ -238,24 +247,42 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDEEAF6"/>
-        <bgColor rgb="FFDEEAF6"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -280,21 +307,15 @@
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -513,165 +534,313 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr defaultColWidth="47" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="32.26953125" customWidth="1"/>
-    <col min="2" max="2" width="27.1796875" customWidth="1"/>
+    <col min="1" max="16384" width="47" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" s="10" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+    </row>
+    <row r="2" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
+    <row r="4" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6" ht="15.75" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B11" s="4" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="8" t="s">
+      <c r="C11" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="8" t="s">
+      <c r="C12" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A13" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A14" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="C14" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A15" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="4"/>
-      <c r="B16" s="5"/>
-    </row>
-    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-    </row>
-    <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A16" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A17" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+    </row>
+    <row r="23" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A23" s="6"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+    </row>
+    <row r="24" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A26" s="6"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -682,13 +851,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{608DC02D-A3BC-4E94-A0C9-91816C3DAF43}">
   <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="58.453125" customWidth="1"/>
-    <col min="2" max="2" width="19.81640625" customWidth="1"/>
+    <col min="1" max="1" width="58.42578125" customWidth="1"/>
+    <col min="2" max="2" width="19.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -696,82 +865,82 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="13" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="12.95">
+      <c r="A2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="B5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/CardiauFflachCemeg.xlsx
+++ b/CardiauFflachCemeg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD624D91-E9C6-4920-9A5F-E01A64C80668}"/>
+  <xr:revisionPtr revIDLastSave="64" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24624DE2-318F-4223-86A3-011A01DB8476}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="60">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -154,6 +154,9 @@
   </si>
   <si>
     <t>Adeiledd_graffen</t>
+  </si>
+  <si>
+    <t>Disgrifiwch ac eglurwch ymdoddbwynt a berwbwynt adeiledd Ionig Enfawr</t>
   </si>
   <si>
     <t>Delwedd</t>
@@ -304,18 +307,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -537,48 +552,49 @@
   <dimension ref="A1:F26"/>
   <sheetFormatPr defaultColWidth="47" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="16384" width="47" style="7"/>
+    <col min="1" max="1" width="47" style="14"/>
+    <col min="2" max="16384" width="47" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="10" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:6" s="12" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="5" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="6" t="s">
         <v>8</v>
       </c>
     </row>
@@ -586,13 +602,13 @@
       <c r="A4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="5" t="s">
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="6" t="s">
         <v>11</v>
       </c>
     </row>
@@ -600,247 +616,249 @@
       <c r="A5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4" t="s">
+      <c r="C5" s="5"/>
+      <c r="D5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
     </row>
     <row r="6" spans="1:6" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4" t="s">
+      <c r="C6" s="5"/>
+      <c r="D6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
     </row>
     <row r="7" spans="1:6" ht="15.75" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
     </row>
     <row r="8" spans="1:6" ht="15.75" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
     </row>
     <row r="9" spans="1:6" ht="15.75" customHeight="1">
       <c r="A9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
     </row>
     <row r="10" spans="1:6" ht="15.75" customHeight="1">
       <c r="A10" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1">
       <c r="A11" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
     </row>
     <row r="12" spans="1:6" ht="15.75" customHeight="1">
       <c r="A12" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
     </row>
     <row r="13" spans="1:6" ht="15.75" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
     </row>
     <row r="14" spans="1:6" ht="15.75" customHeight="1">
       <c r="A14" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
     </row>
     <row r="15" spans="1:6" ht="15.75" customHeight="1">
       <c r="A15" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
     </row>
     <row r="16" spans="1:6" ht="15.75" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
     </row>
     <row r="17" spans="1:6" ht="15.75" customHeight="1">
       <c r="A17" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
+      <c r="A18" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
     </row>
     <row r="19" spans="1:6" ht="15.75" customHeight="1">
       <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
     </row>
     <row r="20" spans="1:6" ht="15.75" customHeight="1">
       <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
     </row>
     <row r="21" spans="1:6" ht="15.75" customHeight="1">
       <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
+      <c r="A22" s="7"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
     </row>
     <row r="23" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
+      <c r="A23" s="7"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
+      <c r="A24" s="7"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
     </row>
     <row r="25" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
+      <c r="A25" s="7"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
     </row>
     <row r="26" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A26" s="6"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
+      <c r="A26" s="7"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -865,82 +883,82 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="12.95">
       <c r="A2" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/CardiauFflachCemeg.xlsx
+++ b/CardiauFflachCemeg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="64" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24624DE2-318F-4223-86A3-011A01DB8476}"/>
+  <xr:revisionPtr revIDLastSave="72" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58E1881E-1F5D-48BF-9EC6-5BDA5646799D}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="59">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -45,7 +45,7 @@
     <t>Ateb</t>
   </si>
   <si>
-    <t>Delwedd Cwestiwn</t>
+    <t>Delwedd</t>
   </si>
   <si>
     <t>Delwedd Ateb</t>
@@ -117,49 +117,46 @@
     <t>Ionig Enfawr</t>
   </si>
   <si>
-    <t>Adeiledd_ionig</t>
+    <t>Adeiledd_ionig.png</t>
   </si>
   <si>
     <t>Diemwnt</t>
   </si>
   <si>
-    <t>Adeiledd_Diemwnt</t>
+    <t>Adeiledd_Diemwnt.png</t>
   </si>
   <si>
     <t>Graffit</t>
   </si>
   <si>
-    <t>Adeiledd_graffit</t>
+    <t>Adeiledd_graffit.png</t>
   </si>
   <si>
     <t>Buckminster Ffwleren</t>
   </si>
   <si>
-    <t>Adeiledd_Buckminsterffwleren</t>
+    <t>Adeiledd_Buckminsterffwleren.png</t>
   </si>
   <si>
     <t>Moleciwlaidd Syml</t>
   </si>
   <si>
-    <t>Adeiledd_moleciwlaidd_syml</t>
+    <t>Adeiledd_moleciwlaidd_syml.png</t>
   </si>
   <si>
     <t>Nanotiwb carbon</t>
   </si>
   <si>
-    <t>Adeiledd_nanotiwb_carbon</t>
+    <t>Adeiledd_nanotiwb_carbon.png</t>
   </si>
   <si>
     <t>Graffen</t>
   </si>
   <si>
-    <t>Adeiledd_graffen</t>
+    <t>Adeiledd_graffen.png</t>
   </si>
   <si>
     <t>Disgrifiwch ac eglurwch ymdoddbwynt a berwbwynt adeiledd Ionig Enfawr</t>
-  </si>
-  <si>
-    <t>Delwedd</t>
   </si>
   <si>
     <t>Beth sy'n fesur o inertia gwrthrych?</t>
@@ -883,82 +880,82 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="12.95">
       <c r="A2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" t="s">
         <v>44</v>
-      </c>
-      <c r="B3" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" t="s">
         <v>46</v>
-      </c>
-      <c r="B4" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" t="s">
         <v>48</v>
-      </c>
-      <c r="B5" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" t="s">
         <v>50</v>
-      </c>
-      <c r="B6" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" t="s">
         <v>52</v>
-      </c>
-      <c r="B7" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" t="s">
         <v>54</v>
-      </c>
-      <c r="B8" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" t="s">
         <v>56</v>
-      </c>
-      <c r="B9" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" t="s">
         <v>58</v>
-      </c>
-      <c r="B10" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/CardiauFflachCemeg.xlsx
+++ b/CardiauFflachCemeg.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="72" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58E1881E-1F5D-48BF-9EC6-5BDA5646799D}"/>
+  <xr:revisionPtr revIDLastSave="103" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAABA74E-CDE9-42A1-B9F4-9B43E19DAD14}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="5.1 Cemeg uned 1" sheetId="1" r:id="rId1"/>
-    <sheet name="5.2 Cemeg uned 2" sheetId="3" r:id="rId2"/>
+    <sheet name="5.1 Cemeg uned Bondio" sheetId="1" r:id="rId1"/>
+    <sheet name="5.2 Cemeg uned Asidau" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="49">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -45,7 +45,7 @@
     <t>Ateb</t>
   </si>
   <si>
-    <t>Delwedd</t>
+    <t>Delwedd Cwestiwn</t>
   </si>
   <si>
     <t>Delwedd Ateb</t>
@@ -81,7 +81,7 @@
     <t>Mae'r electron o blisgyn allanol y sodiwm yn cael ei golli i blisgyn allanol y clorin.</t>
   </si>
   <si>
-    <t>Bondio_NaCl</t>
+    <t>Bondio_NaCl.png</t>
   </si>
   <si>
     <t>Gwnewch ddiagram o'r ionau sodiwm a clorin sy'n ffurfio pan fydd atom sodiwm (Na 2.8.1) a clorin (Cl 2.8.7) yn bondio.</t>
@@ -90,7 +90,7 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Ionau_Na_a_Cl</t>
+    <t>Ionau_Na_a_Cl.png</t>
   </si>
   <si>
     <t>Beth yw adeiledd electronig yr ionau sodiwm a clorin sy'n ffurfio pan fydd atom sodiwm (Na 2.8.1) a clorin (Cl 2.8.7) yn bondio?</t>
@@ -159,68 +159,38 @@
     <t>Disgrifiwch ac eglurwch ymdoddbwynt a berwbwynt adeiledd Ionig Enfawr</t>
   </si>
   <si>
-    <t>Beth sy'n fesur o inertia gwrthrych?</t>
-  </si>
-  <si>
-    <t>Màs y gwrthrych.</t>
-  </si>
-  <si>
-    <t>à</t>
-  </si>
-  <si>
-    <t>Beth yw ystyr buanedd terfynol?</t>
-  </si>
-  <si>
-    <t>Buanedd [neu gyflymder] uchaf  pan fydd y grymoedd yn gytbwys.</t>
-  </si>
-  <si>
-    <t>Nodwch deddf gyntaf mudiant Newton.</t>
-  </si>
-  <si>
-    <t>Bydd gwrthrych yn parhau’n ddisymud (at rest), neu’n symud ar gyflymder cyson, os yw’r grymoedd arno yn gytbwys.</t>
-  </si>
-  <si>
-    <t>Nodwch ail ddeddf  mudiant Newton.</t>
-  </si>
-  <si>
-    <t>grym cydeffaith = màs x cyflymiad</t>
-  </si>
-  <si>
-    <t>Nodwch trydedd ddeddf  mudiant Newton.</t>
-  </si>
-  <si>
-    <t>Os yw corff A yn rhoi grym ar corff B, yna bydd corff B yn rhoi grym hafal a dirgroes ar corff A.</t>
-  </si>
-  <si>
-    <t>Enwch y ddau rym sydd yn gweithredu ar wrthrych sydd yn syrthio drwy'r aer?</t>
-  </si>
-  <si>
-    <t>Disgyrchiant (neu pwysau) a gwrthiant aer.</t>
-  </si>
-  <si>
-    <t>Mae plymiwr awyr yn neidio allan o awyren, beth sy'n digwydd i'r gwrthiant aer arno fel mae'n syrthio?</t>
-  </si>
-  <si>
-    <t>Cynyddu</t>
-  </si>
-  <si>
-    <t>Mae plymiwr awyr yn neidio allan o awyren, beth sy'n digwydd i'w bwysau fel mae'n syrthio?</t>
-  </si>
-  <si>
-    <t>Aros yn gyson</t>
-  </si>
-  <si>
-    <t>Disgrifiwch fudiant plymiwr awyr os yw'r gwrthiant aer arno yn  hafal i'w bwysau (grym disgyrchaint)?</t>
-  </si>
-  <si>
-    <t>Buaned cyson neu cyflymder cyson (buanedd terfynol)</t>
+    <t>UCHEL - bondiau ionig cryf rhwng yr ionau</t>
+  </si>
+  <si>
+    <t>Disgrifiwch ac eglurwch ymdoddbwynt a berwbwynt adeiledd moleciwlaidd syml</t>
+  </si>
+  <si>
+    <t>ISEL - grymoedd gwan rhwng y moleciwlau</t>
+  </si>
+  <si>
+    <t>Disgrifiwch ac eglurwch ymdoddbwynt a berwbwynt adeiledd cofalent enfawr - Graffit a Diemwnt</t>
+  </si>
+  <si>
+    <t>UCHEL - bondiau icofalent cryf rhwng yr atomau i gyd</t>
+  </si>
+  <si>
+    <t>Disgrifiwch ac eglurwch ymdoddbwynt a berwbwynt adeiledd Ionig Metelig</t>
+  </si>
+  <si>
+    <t>UCHEL - bondiau metelig cryf rhwng yr ionau positif a'r môr o electronau rhydd</t>
+  </si>
+  <si>
+    <t>Disgrifiwch ac eglurwch hydoddedd adeiledd Ionig Enfawr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDAWDD - ionau positif a negatif yn gwahanu wrth i foleciwlau dŵr </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -229,22 +199,9 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
@@ -304,25 +261,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -549,313 +504,331 @@
   <dimension ref="A1:F26"/>
   <sheetFormatPr defaultColWidth="47" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="47" style="14"/>
-    <col min="2" max="16384" width="47" style="9"/>
+    <col min="1" max="1" width="47" style="12"/>
+    <col min="2" max="16384" width="47" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="12" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:6" s="10" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="6" t="s">
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="6" t="s">
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5" t="s">
+      <c r="C5" s="3"/>
+      <c r="D5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5" t="s">
+      <c r="C6" s="3"/>
+      <c r="D6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
     </row>
     <row r="7" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
     </row>
     <row r="8" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
     </row>
     <row r="9" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
     </row>
     <row r="12" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
     </row>
     <row r="13" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
     </row>
     <row r="14" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
     </row>
     <row r="15" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
     </row>
     <row r="16" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
     </row>
     <row r="17" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
     </row>
     <row r="18" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
+      <c r="B18" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
     </row>
     <row r="19" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A19" s="4"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
+      <c r="A19" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
     </row>
     <row r="20" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A20" s="4"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
+      <c r="A20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
     </row>
     <row r="21" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A21" s="4"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
+      <c r="A21" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A22" s="7"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
+      <c r="A22" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
     </row>
     <row r="23" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A23" s="7"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
+      <c r="A23" s="5"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A24" s="7"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
+      <c r="A24" s="5"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
     </row>
     <row r="25" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A25" s="7"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
+      <c r="A25" s="5"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
     </row>
     <row r="26" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A26" s="7"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
+      <c r="A26" s="5"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -865,99 +838,61 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{608DC02D-A3BC-4E94-A0C9-91816C3DAF43}">
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="12.6"/>
+  <dimension ref="A1:F32"/>
+  <sheetFormatPr defaultRowHeight="12.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="58.42578125" customWidth="1"/>
-    <col min="2" max="2" width="19.85546875" customWidth="1"/>
+    <col min="1" max="4" width="49.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="12.95">
-      <c r="A2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
-        <v>55</v>
-      </c>
-      <c r="B9" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
-        <v>57</v>
-      </c>
-      <c r="B10" t="s">
-        <v>58</v>
-      </c>
-    </row>
+      <c r="D1" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+    </row>
+    <row r="2" spans="1:6" ht="25.5" customHeight="1">
+      <c r="D2" s="1"/>
+    </row>
+    <row r="3" spans="1:6" ht="25.5" customHeight="1"/>
+    <row r="4" spans="1:6" ht="25.5" customHeight="1"/>
+    <row r="5" spans="1:6" ht="25.5" customHeight="1"/>
+    <row r="6" spans="1:6" ht="25.5" customHeight="1"/>
+    <row r="7" spans="1:6" ht="25.5" customHeight="1"/>
+    <row r="8" spans="1:6" ht="25.5" customHeight="1"/>
+    <row r="9" spans="1:6" ht="25.5" customHeight="1"/>
+    <row r="10" spans="1:6" ht="25.5" customHeight="1"/>
+    <row r="11" spans="1:6" ht="25.5" customHeight="1"/>
+    <row r="12" spans="1:6" ht="25.5" customHeight="1"/>
+    <row r="13" spans="1:6" ht="25.5" customHeight="1"/>
+    <row r="14" spans="1:6" ht="25.5" customHeight="1"/>
+    <row r="15" spans="1:6" ht="25.5" customHeight="1"/>
+    <row r="16" spans="1:6" ht="25.5" customHeight="1"/>
+    <row r="17" ht="25.5" customHeight="1"/>
+    <row r="18" ht="25.5" customHeight="1"/>
+    <row r="19" ht="25.5" customHeight="1"/>
+    <row r="20" ht="25.5" customHeight="1"/>
+    <row r="21" ht="25.5" customHeight="1"/>
+    <row r="22" ht="25.5" customHeight="1"/>
+    <row r="23" ht="25.5" customHeight="1"/>
+    <row r="24" ht="25.5" customHeight="1"/>
+    <row r="25" ht="25.5" customHeight="1"/>
+    <row r="26" ht="25.5" customHeight="1"/>
+    <row r="27" ht="25.5" customHeight="1"/>
+    <row r="28" ht="25.5" customHeight="1"/>
+    <row r="29" ht="25.5" customHeight="1"/>
+    <row r="30" ht="25.5" customHeight="1"/>
+    <row r="31" ht="25.5" customHeight="1"/>
+    <row r="32" ht="25.5" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/CardiauFflachCemeg.xlsx
+++ b/CardiauFflachCemeg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="103" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAABA74E-CDE9-42A1-B9F4-9B43E19DAD14}"/>
+  <xr:revisionPtr revIDLastSave="166" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{974E0897-4C8B-43D3-A3C8-59D1D16A6D28}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="80">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -138,6 +138,12 @@
     <t>Adeiledd_Buckminsterffwleren.png</t>
   </si>
   <si>
+    <t>Rhowch ddefnydd a priodwedd sy'n egluro'r defnydd o Buckminster Ffwleren</t>
+  </si>
+  <si>
+    <t>Cario cyffuriau yn y corff - PRIODWEDD: siap cawell (cage) i ddal y cyffur</t>
+  </si>
+  <si>
     <t>Moleciwlaidd Syml</t>
   </si>
   <si>
@@ -150,12 +156,24 @@
     <t>Adeiledd_nanotiwb_carbon.png</t>
   </si>
   <si>
+    <t>Rhowch ddefnydd a priodwedd sy'n egluro'r defnydd o nanotiwb carbon</t>
+  </si>
+  <si>
+    <t>Cylchedau electronig bach iawn (maint nano) - PRIODWEDD: dargludo trydan</t>
+  </si>
+  <si>
     <t>Graffen</t>
   </si>
   <si>
     <t>Adeiledd_graffen.png</t>
   </si>
   <si>
+    <t>Rhowch ddefnydd a priodwedd sy'n egluro'r defnydd o graffen</t>
+  </si>
+  <si>
+    <t>Cylchedau electronig bach iawn (maint nano) - PRIODWEDD: dargludo trydan neu sgrin ffôn - PRIODWEDD: caled a chryf</t>
+  </si>
+  <si>
     <t>Disgrifiwch ac eglurwch ymdoddbwynt a berwbwynt adeiledd Ionig Enfawr</t>
   </si>
   <si>
@@ -183,14 +201,89 @@
     <t>Disgrifiwch ac eglurwch hydoddedd adeiledd Ionig Enfawr</t>
   </si>
   <si>
-    <t xml:space="preserve">HYDAWDD - ionau positif a negatif yn gwahanu wrth i foleciwlau dŵr </t>
+    <t>HYDAWDD - ionau positif a negatif yn gwahanu wrth i'r moleciwlau dŵr eu amgylchynu</t>
+  </si>
+  <si>
+    <t>Pa gyflwr mae adeiledd Ionig Enfawr yn dargludo trydan?</t>
+  </si>
+  <si>
+    <t>Pan mae wedi hydoddi neu yn dawdd (dim yn solid)</t>
+  </si>
+  <si>
+    <t>Eglurwch pam fod adeiledd Ionig Enfawr yn dargludo trydan pan wedi hydoddi neu yn dawdd.</t>
+  </si>
+  <si>
+    <t>Mae'r ionau yn rhydd i symud</t>
+  </si>
+  <si>
+    <t>Disgrifiwch ac eglurwch dargludedd trydanol adeiledd moleciwlaidd syml</t>
+  </si>
+  <si>
+    <t>DIM yn dargludo trydan- dim electronau nac ionau rhydd i symud</t>
+  </si>
+  <si>
+    <t>Disgrifiwch ac eglurwch dargluedd trydanol adeiledd Graffit</t>
+  </si>
+  <si>
+    <t>DARGLUDO - electronau rhydd i symud rhwng yr haenau</t>
+  </si>
+  <si>
+    <t>Disgrifiwch ac eglurwch dargluedd trydanol adeiledd Diemwnt</t>
+  </si>
+  <si>
+    <t>Disgrifiwch ac eglurwch dargluedd trydanol adeiledd metelau</t>
+  </si>
+  <si>
+    <t>DARGLUDO - electronau yn y môr yn rhydd i symud</t>
+  </si>
+  <si>
+    <t>Pam fod Diemwnt yn galed?</t>
+  </si>
+  <si>
+    <t>Bondiau cofalent cryf rhwng yr atomau trwy'r adeiledd</t>
+  </si>
+  <si>
+    <t>Pam fod Graffit yn feddal?</t>
+  </si>
+  <si>
+    <t>Grymoedd GWAN rhwng yr haenau felly HAENAU YN LLITHRO dros ei gilydd</t>
+  </si>
+  <si>
+    <t>Pam fod metelau yn HYDWYTH a HYDRIN?</t>
+  </si>
+  <si>
+    <t>Ionau'n gallu LLITHRO dros ei gilydd</t>
+  </si>
+  <si>
+    <t>Beth yw maint nano gronyn?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-100nm </t>
+  </si>
+  <si>
+    <t>Beth yw priodweddau nano gronynnau arian?</t>
+  </si>
+  <si>
+    <t>gwrthfacteria, gwrthfirws, gwrthffwngws</t>
+  </si>
+  <si>
+    <t>I beth mae nano gronynnau arian yn cael eu defnyddio?</t>
+  </si>
+  <si>
+    <t>plasteri, sanau chwaraeon, leini oergell (fridge), chwistrellydd (spray) diheintio (sterilise)</t>
+  </si>
+  <si>
+    <t>Rhowch 2 ddefnydd a priodwedd sy'n egluro'r defnydd o nanogronynnau titaniwm deuocsid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eli haul </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -204,23 +297,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -228,10 +304,35 @@
       <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
     </font>
   </fonts>
   <fills count="2">
@@ -261,26 +362,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -501,334 +605,459 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultColWidth="47" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="47" style="12"/>
-    <col min="2" max="16384" width="47" style="7"/>
+    <col min="1" max="1" width="47" style="15"/>
+    <col min="2" max="2" width="47" style="14"/>
+    <col min="3" max="16384" width="47" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="10" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:6" s="7" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="4" t="s">
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="4" t="s">
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="12" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3" t="s">
+      <c r="C5" s="10"/>
+      <c r="D5" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
     </row>
     <row r="6" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3" t="s">
+      <c r="C6" s="10"/>
+      <c r="D6" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
     </row>
     <row r="7" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
     </row>
     <row r="8" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
     </row>
     <row r="9" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
     </row>
     <row r="10" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
     </row>
     <row r="12" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
     </row>
     <row r="13" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
     </row>
     <row r="14" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
     </row>
     <row r="15" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+    </row>
+    <row r="16" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A16" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-    </row>
-    <row r="16" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A16" s="2" t="s">
+      <c r="B16" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+    </row>
+    <row r="17" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A17" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-    </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A17" s="2" t="s">
+      <c r="B17" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+    </row>
+    <row r="18" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A18" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+    </row>
+    <row r="19" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A19" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-    </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A18" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-    </row>
-    <row r="19" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A19" s="2" t="s">
+      <c r="B19" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C19" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
     </row>
     <row r="20" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
     </row>
     <row r="21" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
     </row>
     <row r="23" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A23" s="5"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
+      <c r="A23" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A24" s="5"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
+      <c r="A24" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
     </row>
     <row r="25" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A25" s="5"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
+      <c r="A25" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
     </row>
     <row r="26" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A26" s="5"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
+      <c r="A26" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+    </row>
+    <row r="27" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A27" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+    </row>
+    <row r="28" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A28" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+    </row>
+    <row r="29" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A29" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A30" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A31" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A32" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A33" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A34" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A35" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="B35" s="14" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A36" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A37" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A38" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>79</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -845,20 +1074,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
     </row>
     <row r="2" spans="1:6" ht="25.5" customHeight="1">
       <c r="D2" s="1"/>

--- a/CardiauFflachCemeg.xlsx
+++ b/CardiauFflachCemeg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="166" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{974E0897-4C8B-43D3-A3C8-59D1D16A6D28}"/>
+  <xr:revisionPtr revIDLastSave="181" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFF8322D-0FB7-4BCB-A949-91BD14B2B2CD}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="83">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -171,7 +171,7 @@
     <t>Rhowch ddefnydd a priodwedd sy'n egluro'r defnydd o graffen</t>
   </si>
   <si>
-    <t>Cylchedau electronig bach iawn (maint nano) - PRIODWEDD: dargludo trydan neu sgrin ffôn - PRIODWEDD: caled a chryf</t>
+    <t>Cylchedau electronig bach iawn (maint nano) PRIODWEDD: dargludo trydan &lt;br&gt;&lt;br&gt;neu Sgrin ffôn PRIODWEDD: caled a chryf</t>
   </si>
   <si>
     <t>Disgrifiwch ac eglurwch ymdoddbwynt a berwbwynt adeiledd Ionig Enfawr</t>
@@ -276,7 +276,16 @@
     <t>Rhowch 2 ddefnydd a priodwedd sy'n egluro'r defnydd o nanogronynnau titaniwm deuocsid</t>
   </si>
   <si>
-    <t xml:space="preserve">Eli haul </t>
+    <t>Eli haul -  PRIODWEDD: adlewyrchu pelydrau uwchfioled o'r haul&lt;br&gt; Ffenestri hunan-lanhau (self-cleaning) -  PRIODWEDD: torri baw (dirt) i lawr a gadael i ddŵr redeg dros y ffenestr a'i olchi i ffwrdd</t>
+  </si>
+  <si>
+    <t>Enwch y 5 gwahanol ddefnydd clyfar</t>
+  </si>
+  <si>
+    <t>Pigment Thermocromig&lt;br&gt; Pigment Ffotocromig&lt;br&gt; Polymer Cofio Si</t>
+  </si>
+  <si>
+    <t>Rhowch ddefnydd a priodwedd sy'n egluro'r defnydd o Pigment Thermocromig</t>
   </si>
 </sst>
 </file>
@@ -605,12 +614,13 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr defaultColWidth="47" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="47" style="15"/>
     <col min="2" max="2" width="47" style="14"/>
-    <col min="3" max="16384" width="47" style="11"/>
+    <col min="3" max="3" width="33.5703125" style="11" customWidth="1"/>
+    <col min="4" max="16384" width="47" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="7" customFormat="1" ht="15.75" customHeight="1">
@@ -1057,6 +1067,19 @@
       </c>
       <c r="B38" s="14" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A39" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A40" s="15" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/CardiauFflachCemeg.xlsx
+++ b/CardiauFflachCemeg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="181" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFF8322D-0FB7-4BCB-A949-91BD14B2B2CD}"/>
+  <xr:revisionPtr revIDLastSave="212" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71BED555-39BD-4B13-9809-E7CA22B07F49}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="95">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -108,6 +108,15 @@
     <t>Pa fath o fondio sy'n digwydd pan fydd electronau yn cael eu rhannu rhwng 2 atom?</t>
   </si>
   <si>
+    <t>Pa un yw'r diagram cywir i methan $CH_4$ ?</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>Fformiwla_methan</t>
+  </si>
+  <si>
     <t>Pa fath o fondio sy'n digwydd pan fydd ionau positif yn cael eu dal efo'i gilydd gan y Môr o Electronau rhydd?</t>
   </si>
   <si>
@@ -282,10 +291,37 @@
     <t>Enwch y 5 gwahanol ddefnydd clyfar</t>
   </si>
   <si>
-    <t>Pigment Thermocromig&lt;br&gt; Pigment Ffotocromig&lt;br&gt; Polymer Cofio Si</t>
+    <t>Pigment Thermocromig&lt;br&gt;&lt;br&gt;  Pigment Ffotocromig&lt;br&gt;&lt;br&gt;  Polymer Cofio Siâp &lt;br&gt;&lt;br&gt; Aloi Cofio Siâp &lt;br&gt;&lt;br&gt;  Hydrogel</t>
   </si>
   <si>
     <t>Rhowch ddefnydd a priodwedd sy'n egluro'r defnydd o Pigment Thermocromig</t>
+  </si>
+  <si>
+    <t>Mygiau coffi, thermomedr...  &lt;br&gt; PRIODWEDD: Newid lliw yn gildroadwy gyda newid tymheredd</t>
+  </si>
+  <si>
+    <t>Rhowch ddefnydd a priodwedd sy'n egluro'r defnydd o Pigment Ffotocromig</t>
+  </si>
+  <si>
+    <t>Lens sbectol haul...  &lt;br&gt; PRIODWEDD: Newid lliw yn gildroadwy gyda newid mewn arddwysedd (cryfder) golau</t>
+  </si>
+  <si>
+    <t>Rhowch ddefnydd a priodwedd sy'n egluro'r defnydd o Polymer Cofio Siâp</t>
+  </si>
+  <si>
+    <t>Gum shield (tarian geg)...  &lt;br&gt; PRIODWEDD: Adennill ei (mynd yn ôl i'w) siâp gwreiddiol wrth ei wresogi</t>
+  </si>
+  <si>
+    <t>Rhowch ddefnydd a priodwedd sy'n egluro'r defnydd o Aloi Cofio Siâp</t>
+  </si>
+  <si>
+    <t>Sbringiau, 'braces', corff car...  &lt;br&gt; PRIODWEDD: Adennill ei (mynd yn ôl i'w) siâp gwreiddiol wrth ei wresogi</t>
+  </si>
+  <si>
+    <t>Rhowch ddefnydd a priodwedd sy'n egluro'r defnydd o Hydrogel</t>
+  </si>
+  <si>
+    <t>Clwt babi (nappies) &lt;br&gt; PRIODWEDD: amsugno dŵr gan gynyddu ei gyfaint ond crebachu yn ôl gyda newid mewn tymheredd</t>
   </si>
 </sst>
 </file>
@@ -614,7 +650,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr defaultColWidth="47" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="47" style="15"/>
@@ -748,36 +784,36 @@
         <v>23</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="10"/>
+        <v>24</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>25</v>
+      </c>
       <c r="D10" s="10"/>
       <c r="E10" s="10"/>
       <c r="F10" s="10"/>
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1">
       <c r="A11" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>26</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C11" s="10"/>
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
       <c r="F11" s="10"/>
     </row>
     <row r="12" spans="1:6" ht="15.75" customHeight="1">
       <c r="A12" s="8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -785,13 +821,13 @@
     </row>
     <row r="13" spans="1:6" ht="15.75" customHeight="1">
       <c r="A13" s="8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
@@ -799,13 +835,13 @@
     </row>
     <row r="14" spans="1:6" ht="15.75" customHeight="1">
       <c r="A14" s="8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
@@ -813,39 +849,39 @@
     </row>
     <row r="15" spans="1:6" ht="15.75" customHeight="1">
       <c r="A15" s="8" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="10"/>
+      <c r="C15" s="10" t="s">
+        <v>35</v>
+      </c>
       <c r="D15" s="10"/>
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
     </row>
     <row r="16" spans="1:6" ht="15.75" customHeight="1">
       <c r="A16" s="8" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>36</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="C16" s="10"/>
       <c r="D16" s="10"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
     </row>
     <row r="17" spans="1:6" ht="15.75" customHeight="1">
       <c r="A17" s="8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="10"/>
@@ -853,48 +889,50 @@
     </row>
     <row r="18" spans="1:6" ht="15.75" customHeight="1">
       <c r="A18" s="8" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="10"/>
+      <c r="C18" s="10" t="s">
+        <v>41</v>
+      </c>
       <c r="D18" s="10"/>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
     </row>
     <row r="19" spans="1:6" ht="15.75" customHeight="1">
       <c r="A19" s="8" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>42</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="C19" s="10"/>
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
     </row>
     <row r="20" spans="1:6" ht="15.75" customHeight="1">
       <c r="A20" s="8" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="10"/>
+      <c r="C20" s="10" t="s">
+        <v>45</v>
+      </c>
       <c r="D20" s="10"/>
       <c r="E20" s="10"/>
       <c r="F20" s="10"/>
     </row>
     <row r="21" spans="1:6" ht="15.75" customHeight="1">
       <c r="A21" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="10"/>
@@ -903,10 +941,10 @@
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1">
       <c r="A22" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C22" s="10"/>
       <c r="D22" s="10"/>
@@ -915,10 +953,10 @@
     </row>
     <row r="23" spans="1:6" ht="15.75" customHeight="1">
       <c r="A23" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="10"/>
@@ -927,10 +965,10 @@
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1">
       <c r="A24" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
@@ -939,22 +977,22 @@
     </row>
     <row r="25" spans="1:6" ht="15.75" customHeight="1">
       <c r="A25" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
+        <v>55</v>
+      </c>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
     </row>
     <row r="26" spans="1:6" ht="15.75" customHeight="1">
       <c r="A26" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
@@ -963,10 +1001,10 @@
     </row>
     <row r="27" spans="1:6" ht="15.75" customHeight="1">
       <c r="A27" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
@@ -975,10 +1013,10 @@
     </row>
     <row r="28" spans="1:6" ht="15.75" customHeight="1">
       <c r="A28" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
@@ -987,10 +1025,10 @@
     </row>
     <row r="29" spans="1:6" ht="15.75" customHeight="1">
       <c r="A29" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
@@ -999,87 +1037,134 @@
     </row>
     <row r="30" spans="1:6" ht="15.75" customHeight="1">
       <c r="A30" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B30" s="14" t="s">
-        <v>60</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
     </row>
     <row r="31" spans="1:6" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A32" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="B32" s="14" t="s">
+      <c r="A32" s="8" t="s">
         <v>67</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="15.75" customHeight="1">
       <c r="A33" s="15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="15.75" customHeight="1">
       <c r="A34" s="15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="15.75" customHeight="1">
       <c r="A35" s="15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="15.75" customHeight="1">
       <c r="A36" s="15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="15.75" customHeight="1">
       <c r="A37" s="15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="15.75" customHeight="1">
       <c r="A38" s="15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="15.75" customHeight="1">
       <c r="A39" s="15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B39" s="14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="15.75" customHeight="1">
       <c r="A40" s="15" t="s">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A41" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A42" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A43" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A44" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A45" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="B45" s="14" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/CardiauFflachCemeg.xlsx
+++ b/CardiauFflachCemeg.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GriffithsR144\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="212" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71BED555-39BD-4B13-9809-E7CA22B07F49}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B01AA81B-939E-4DFA-BEB7-1C1A38F98F08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -114,9 +114,6 @@
     <t>B</t>
   </si>
   <si>
-    <t>Fformiwla_methan</t>
-  </si>
-  <si>
     <t>Pa fath o fondio sy'n digwydd pan fydd ionau positif yn cael eu dal efo'i gilydd gan y Môr o Electronau rhydd?</t>
   </si>
   <si>
@@ -322,6 +319,9 @@
   </si>
   <si>
     <t>Clwt babi (nappies) &lt;br&gt; PRIODWEDD: amsugno dŵr gan gynyddu ei gyfaint ond crebachu yn ôl gyda newid mewn tymheredd</t>
+  </si>
+  <si>
+    <t>Fformiwla_methan.png</t>
   </si>
 </sst>
 </file>
@@ -410,25 +410,25 @@
   <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -655,7 +655,7 @@
   <cols>
     <col min="1" max="1" width="47" style="15"/>
     <col min="2" max="2" width="47" style="14"/>
-    <col min="3" max="3" width="33.5703125" style="11" customWidth="1"/>
+    <col min="3" max="3" width="33.54296875" style="11" customWidth="1"/>
     <col min="4" max="16384" width="47" style="11"/>
   </cols>
   <sheetData>
@@ -787,7 +787,7 @@
         <v>24</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>25</v>
+        <v>94</v>
       </c>
       <c r="D10" s="10"/>
       <c r="E10" s="10"/>
@@ -795,7 +795,7 @@
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1">
       <c r="A11" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>10</v>
@@ -807,13 +807,13 @@
     </row>
     <row r="12" spans="1:6" ht="15.75" customHeight="1">
       <c r="A12" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="C12" s="10" t="s">
         <v>28</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>29</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -821,13 +821,13 @@
     </row>
     <row r="13" spans="1:6" ht="15.75" customHeight="1">
       <c r="A13" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B13" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>30</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>31</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
@@ -835,13 +835,13 @@
     </row>
     <row r="14" spans="1:6" ht="15.75" customHeight="1">
       <c r="A14" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B14" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="10" t="s">
         <v>32</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>33</v>
       </c>
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
@@ -849,13 +849,13 @@
     </row>
     <row r="15" spans="1:6" ht="15.75" customHeight="1">
       <c r="A15" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B15" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="10" t="s">
         <v>34</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>35</v>
       </c>
       <c r="D15" s="10"/>
       <c r="E15" s="10"/>
@@ -863,10 +863,10 @@
     </row>
     <row r="16" spans="1:6" ht="15.75" customHeight="1">
       <c r="A16" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="9" t="s">
         <v>36</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>37</v>
       </c>
       <c r="C16" s="10"/>
       <c r="D16" s="10"/>
@@ -875,13 +875,13 @@
     </row>
     <row r="17" spans="1:6" ht="15.75" customHeight="1">
       <c r="A17" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B17" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="10" t="s">
         <v>38</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>39</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="10"/>
@@ -889,13 +889,13 @@
     </row>
     <row r="18" spans="1:6" ht="15.75" customHeight="1">
       <c r="A18" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="10" t="s">
         <v>40</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>41</v>
       </c>
       <c r="D18" s="10"/>
       <c r="E18" s="10"/>
@@ -903,10 +903,10 @@
     </row>
     <row r="19" spans="1:6" ht="15.75" customHeight="1">
       <c r="A19" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="9" t="s">
         <v>42</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>43</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>
@@ -915,13 +915,13 @@
     </row>
     <row r="20" spans="1:6" ht="15.75" customHeight="1">
       <c r="A20" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="10" t="s">
         <v>44</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>45</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="10"/>
@@ -929,10 +929,10 @@
     </row>
     <row r="21" spans="1:6" ht="15.75" customHeight="1">
       <c r="A21" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="9" t="s">
         <v>46</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>47</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="10"/>
@@ -941,10 +941,10 @@
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1">
       <c r="A22" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="9" t="s">
         <v>48</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>49</v>
       </c>
       <c r="C22" s="10"/>
       <c r="D22" s="10"/>
@@ -953,10 +953,10 @@
     </row>
     <row r="23" spans="1:6" ht="15.75" customHeight="1">
       <c r="A23" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" s="9" t="s">
         <v>50</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>51</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="10"/>
@@ -965,10 +965,10 @@
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1">
       <c r="A24" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" s="9" t="s">
         <v>52</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>53</v>
       </c>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
@@ -977,10 +977,10 @@
     </row>
     <row r="25" spans="1:6" ht="15.75" customHeight="1">
       <c r="A25" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" s="9" t="s">
         <v>54</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>55</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="10"/>
@@ -989,10 +989,10 @@
     </row>
     <row r="26" spans="1:6" ht="15.75" customHeight="1">
       <c r="A26" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B26" s="9" t="s">
         <v>56</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>57</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="27" spans="1:6" ht="15.75" customHeight="1">
       <c r="A27" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B27" s="9" t="s">
         <v>58</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>59</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
@@ -1013,10 +1013,10 @@
     </row>
     <row r="28" spans="1:6" ht="15.75" customHeight="1">
       <c r="A28" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B28" s="9" t="s">
         <v>60</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>61</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
@@ -1025,10 +1025,10 @@
     </row>
     <row r="29" spans="1:6" ht="15.75" customHeight="1">
       <c r="A29" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B29" s="9" t="s">
         <v>62</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>63</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
@@ -1037,10 +1037,10 @@
     </row>
     <row r="30" spans="1:6" ht="15.75" customHeight="1">
       <c r="A30" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B30" s="9" t="s">
         <v>64</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>65</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
@@ -1049,122 +1049,122 @@
     </row>
     <row r="31" spans="1:6" ht="15.75" customHeight="1">
       <c r="A31" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" customHeight="1">
       <c r="A32" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B32" s="9" t="s">
         <v>67</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="15.75" customHeight="1">
       <c r="A33" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="B33" s="14" t="s">
         <v>69</v>
-      </c>
-      <c r="B33" s="14" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="15.75" customHeight="1">
       <c r="A34" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="B34" s="14" t="s">
         <v>71</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="15.75" customHeight="1">
       <c r="A35" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="B35" s="14" t="s">
         <v>73</v>
-      </c>
-      <c r="B35" s="14" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="15.75" customHeight="1">
       <c r="A36" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="B36" s="14" t="s">
         <v>75</v>
-      </c>
-      <c r="B36" s="14" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="15.75" customHeight="1">
       <c r="A37" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="B37" s="14" t="s">
         <v>77</v>
-      </c>
-      <c r="B37" s="14" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="15.75" customHeight="1">
       <c r="A38" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="B38" s="14" t="s">
         <v>79</v>
-      </c>
-      <c r="B38" s="14" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="15.75" customHeight="1">
       <c r="A39" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="B39" s="14" t="s">
         <v>81</v>
-      </c>
-      <c r="B39" s="14" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="15.75" customHeight="1">
       <c r="A40" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="B40" s="14" t="s">
         <v>83</v>
-      </c>
-      <c r="B40" s="14" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="15.75" customHeight="1">
       <c r="A41" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="B41" s="14" t="s">
         <v>85</v>
-      </c>
-      <c r="B41" s="14" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="15.75" customHeight="1">
       <c r="A42" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="B42" s="14" t="s">
         <v>87</v>
-      </c>
-      <c r="B42" s="14" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="15.75" customHeight="1">
       <c r="A43" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="B43" s="14" t="s">
         <v>89</v>
-      </c>
-      <c r="B43" s="14" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="15.75" customHeight="1">
       <c r="A44" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="B44" s="14" t="s">
         <v>91</v>
-      </c>
-      <c r="B44" s="14" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="15.75" customHeight="1">
       <c r="A45" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="B45" s="14" t="s">
         <v>93</v>
-      </c>
-      <c r="B45" s="14" t="s">
-        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -1178,7 +1178,7 @@
   <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="12.75" customHeight="1"/>
   <cols>
-    <col min="1" max="4" width="49.42578125" customWidth="1"/>
+    <col min="1" max="4" width="49.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="25.5" customHeight="1">

--- a/CardiauFflachCemeg.xlsx
+++ b/CardiauFflachCemeg.xlsx
@@ -1,20 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GriffithsR144\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B01AA81B-939E-4DFA-BEB7-1C1A38F98F08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="381" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A527BE69-D69B-4138-9C53-B4E96BB5849D}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="5.1 Cemeg uned Bondio" sheetId="1" r:id="rId1"/>
-    <sheet name="5.2 Cemeg uned Asidau" sheetId="3" r:id="rId2"/>
+    <sheet name="5.1 Bondio" sheetId="1" r:id="rId1"/>
+    <sheet name="5.2 Asidau" sheetId="3" r:id="rId2"/>
+    <sheet name="5.3 Metelau (dim electrolysis)" sheetId="4" r:id="rId3"/>
+    <sheet name="5.3 Metelau (electrolysis)" sheetId="5" r:id="rId4"/>
+    <sheet name="5.4 Egni" sheetId="6" r:id="rId5"/>
+    <sheet name="5.5 Olew Crai" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -37,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="172">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -114,6 +118,9 @@
     <t>B</t>
   </si>
   <si>
+    <t>Fformiwla_methan.png</t>
+  </si>
+  <si>
     <t>Pa fath o fondio sy'n digwydd pan fydd ionau positif yn cael eu dal efo'i gilydd gan y Môr o Electronau rhydd?</t>
   </si>
   <si>
@@ -321,14 +328,299 @@
     <t>Clwt babi (nappies) &lt;br&gt; PRIODWEDD: amsugno dŵr gan gynyddu ei gyfaint ond crebachu yn ôl gyda newid mewn tymheredd</t>
   </si>
   <si>
-    <t>Fformiwla_methan.png</t>
+    <t>Pa rif a lliw ar y raddfa pH yw niwtral?</t>
+  </si>
+  <si>
+    <t>7&lt;br&gt; gwyrdd</t>
+  </si>
+  <si>
+    <t>Pa rif a lliw ar y raddfa pH yw asid cryf?</t>
+  </si>
+  <si>
+    <t>0-2&lt;br&gt;coch</t>
+  </si>
+  <si>
+    <t>Pa rif a lliw ar y raddfa pH yw asid gwan?</t>
+  </si>
+  <si>
+    <t>3-6 &lt;br&gt;oren-melyn</t>
+  </si>
+  <si>
+    <t>Pa rif a lliw ar y raddfa pH yw alcali gwan?</t>
+  </si>
+  <si>
+    <t>8-10&lt;br&gt;gwyrdd-las i glas</t>
+  </si>
+  <si>
+    <t>Pa rif a lliw ar y raddfa pH yw alcali cryf?</t>
+  </si>
+  <si>
+    <t>11-14&lt;br&gt;porffor</t>
+  </si>
+  <si>
+    <t>Beth yw enw'r adwaith pan mae asid yn adweithio efo alcali?</t>
+  </si>
+  <si>
+    <t>Niwtraleiddio</t>
+  </si>
+  <si>
+    <t>Beth yw cynhyrchion yr adwaith rhwng&lt;br&gt;&lt;br&gt;ASID     +        METEL&lt;br&gt;&lt;br&gt; a beth yw'r ARSYLWADAU?</t>
+  </si>
+  <si>
+    <t>HALWYN     +     HYDROGEN&lt;br&gt;&lt;br&gt; Arsylwadau&lt;br&gt;eferwi (ffisian) oherwydd hydrogen</t>
+  </si>
+  <si>
+    <t>Beth yw cynhyrchion yr adwaith rhwng&lt;br&gt;&lt;br&gt;ASID     +        BAS (OCSID)&lt;br&gt;&lt;br&gt; a beth yw'r ARSYLWADAU?</t>
+  </si>
+  <si>
+    <t>HALWYN     +     DWR&lt;br&gt;&lt;br&gt; Arsylwadau&lt;br&gt;tymheredd yn cynyddu&lt;br&gt;hydoddiant glas os mai COPR ocsid sy'n adweithio</t>
+  </si>
+  <si>
+    <t>Beth yw cynhyrchion yr adwaith rhwng&lt;br&gt;&lt;br&gt;ASID     +        ALCALI (HYDROCSID)&lt;br&gt;&lt;br&gt; a beth yw'r ARSYLWADAU?</t>
+  </si>
+  <si>
+    <t>HALWYN     +     DŴR&lt;br&gt;&lt;br&gt; Arsylwadau&lt;br&gt;tymheredd yn cynyddu</t>
+  </si>
+  <si>
+    <t>HALWYN     +     DWR    +    CARBON DEUOCSID&lt;br&gt;&lt;br&gt;Arsylwadau&lt;br&gt;eferwi (ffisian) oherwydd carbon deuocsid&lt;br&gt;hydoddiant glas os mai COPR ocsid sy'n adweithio</t>
+  </si>
+  <si>
+    <t>Beth yw ail enw'r halwyn sy'n ffurfio o Asid Hydroclorig?</t>
+  </si>
+  <si>
+    <t>CLORID</t>
+  </si>
+  <si>
+    <t>Beth yw ail enw'r halwyn sy'n ffurfio o Asid Sylffwrig?</t>
+  </si>
+  <si>
+    <t>SYLFFAD</t>
+  </si>
+  <si>
+    <t>Beth yw ail enw'r halwyn sy'n ffurfio o Asid Nitrig?</t>
+  </si>
+  <si>
+    <t>NITRAD</t>
+  </si>
+  <si>
+    <t>Beth yw cynhyrchion yr adwaith:&lt;br&gt;&lt;br&gt; magnesiwm     +     asid hydroclorig</t>
+  </si>
+  <si>
+    <t>magnesiwm clorid     +     hydrogen</t>
+  </si>
+  <si>
+    <t>Beth yw cynhyrchion yr adwaith:&lt;br&gt;&lt;br&gt; haearn     +     asid sylffwrig</t>
+  </si>
+  <si>
+    <t>haearn sylffad    +     hydrogen</t>
+  </si>
+  <si>
+    <t>Beth yw cynhyrchion yr adwaith:&lt;br&gt;&lt;br&gt; sinc     +     asid nitrig</t>
+  </si>
+  <si>
+    <t>sinc nitrad   +     hydrogen</t>
+  </si>
+  <si>
+    <t>Beth yw cynhyrchion yr adwaith:&lt;br&gt;&lt;br&gt; magnesiwm ocsid     +     asid hydroclorig</t>
+  </si>
+  <si>
+    <t>magnesiwm clorid     +     dŵr</t>
+  </si>
+  <si>
+    <t>Beth yw cynhyrchion yr adwaith:&lt;br&gt;&lt;br&gt; copr ocsid    +     asid sylffwrig</t>
+  </si>
+  <si>
+    <t>haearn sylffad    +     dŵr</t>
+  </si>
+  <si>
+    <t>Beth yw cynhyrchion yr adwaith:&lt;br&gt;&lt;br&gt; sinc ocsid     +     asid nitrig</t>
+  </si>
+  <si>
+    <t>sinc nitrad   +     dŵr</t>
+  </si>
+  <si>
+    <t>Beth yw cynhyrchion yr adwaith:&lt;br&gt;&lt;br&gt; sodiwm hydrocsid    +     asid hydroclorig</t>
+  </si>
+  <si>
+    <t>sodiwm clorid     +     dŵr</t>
+  </si>
+  <si>
+    <t>Beth yw cynhyrchion yr adwaith:&lt;br&gt;&lt;br&gt; lithiwm hydrocsid    +     asid sylffwrig</t>
+  </si>
+  <si>
+    <t>lithiwm sylffad    +     dŵr</t>
+  </si>
+  <si>
+    <t>Beth yw cynhyrchion yr adwaith:&lt;br&gt;&lt;br&gt; potasiwm hydrocsid    +     asid nitrig</t>
+  </si>
+  <si>
+    <t>potasiwm nitrad   +     dŵr</t>
+  </si>
+  <si>
+    <t>Beth yw cynhyrchion yr adwaith:&lt;br&gt;&lt;br&gt; sodiwm carbonad      +     asid hydroclorig</t>
+  </si>
+  <si>
+    <t>sodiwm clorid     +     dŵr     +      carbon deuocsid</t>
+  </si>
+  <si>
+    <t>Beth yw cynhyrchion yr adwaith:&lt;br&gt;&lt;br&gt; copr carbonad    +     asid sylffwrig</t>
+  </si>
+  <si>
+    <t>copr sylffad    +     dŵr      +       carbon deuocsid</t>
+  </si>
+  <si>
+    <t>Beth yw cynhyrchion yr adwaith:&lt;br&gt;&lt;br&gt; magnesiwm carbonad   +     asid nitrig</t>
+  </si>
+  <si>
+    <t>magnesiwm nitrad   +     dŵr      +      carbon deuocsid</t>
+  </si>
+  <si>
+    <t>Sut mae gwneud crisialau copr sylffad o copr ocsid neu copr carbonad? ATEB UWCH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhoi asid sylffwrig mewn bicer&lt;br&gt;
+Ychwanegu’r copr carbonad/copr ocsid mewn GORMODEDD tan fydd o yn stopio adweithio er mwyn gofalu bod yr HOLL ASID WEDI ADWEITHIO&lt;br&gt;
+Mi fydd solid i’w weld ar waelod y bicer&lt;br&gt; 
+Ni fydd y carbonad yn parhau i eferwi&lt;br&gt;
+Wrth brofi efo papur pH ni fydd yn asidig&lt;br&gt;
+HIDLO’r solid o’r hydoddiant glas&lt;br&gt;
+GADAEL yr hydoddiant mewn cynnes er mwyn i’r DŴR ANWEDDU’n araf.&lt;br&gt;
+Mi fydd crisialau copr sylffad yn ffurfio.
+</t>
+  </si>
+  <si>
+    <t>Crisialau o halwyn anhydawdd.png</t>
+  </si>
+  <si>
+    <t>Sut mae gwneud crisialau sodiwm clorid o sodiwm hydrocsid ac asid hydroclorig? ATEB UWCH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhoi 25$cm^3$ o’r  alcali sodiwm hydrocsid  mewn fflasg gonigl&lt;br&gt;
+Ychwanegu ychydig o ddiferion (drops) o’r DANGOSYDD&lt;br&gt;
+Rhoi asid hydroclorig yn y BWRED a COFNODI’r darlleniad arno&lt;br&gt;
+Ychwanegu’r asid i’r alcali &lt;br&gt;
+gan droelli’r fflasg er mwyn cymysgu er mwyn iddynt adweithio’n llwyr&lt;br&gt;
+tan fydd y DANGOSYDD yn NEWID LLIW ac felly yr alcali i gyd wedi niwtralu&lt;br&gt;
+COFNODI’r darlleniad ar y bwred eto&lt;br&gt;
+CYFRIFO’r cyfaint o asid sydd wedi ei ychwanegu&lt;br&gt;
+AILADRODD er mwyn cael darlleniadau sy’n debyg&lt;br&gt;
+Cyfrifo’r CYMEDR&lt;br&gt;
+AILADRODD eto HEB Y DANGOSYDD gan ddefnyddio yr un cyfaint o asid ac alcali&lt;br&gt;
+GADAEL yr hydoddiant mewn lle cynnes er mwyn i’r DŴR ANWEDDU’n araf&lt;br&gt;
+Mi fydd crisialau sodiwm clorid yn ffurfio
+</t>
+  </si>
+  <si>
+    <t>Crisialau o halwyn hydawdd.png</t>
+  </si>
+  <si>
+    <t>Sut mae gwneud crisialau copr sylffad o copr ocsid neu copr carbonad? ATEB SYLFAENOL</t>
+  </si>
+  <si>
+    <t>Rhoi GORMODEDD o'r powdr yn yr asid eer mwyn i'r asid i gyd adweithio&lt;br&gt; HIDLO i gael gwared o'r powdr sydd dros ben&lt;br&gt; GADAEL mewn lle CYNNES er mwyn i’r DŴR ANWEDDU</t>
+  </si>
+  <si>
+    <t>Sut mae gwneud crisialau sodiwm clorid o sodiwm hydrocsid ac asid hydroclorig? ATEB SYLFAENOL</t>
+  </si>
+  <si>
+    <t>Rhoi 3 drop o'r DANGOSYDD yn yr alcali&lt;br&gt;Ychwanegu'r ASID o'r BWRED tan mae'r LLIW yn NEWID&lt;br&gt;GADAEL mewn lle CYNNES er mwyn i’r DŴR ANWEDDU</t>
+  </si>
+  <si>
+    <t>Pa fath o adwaith sy'n RHYDDHAU EGNI?</t>
+  </si>
+  <si>
+    <t>ADWAITH ECSOTHERMIG</t>
+  </si>
+  <si>
+    <t>Pa fath o adwaith sy'n AMSUGNO EGNI?</t>
+  </si>
+  <si>
+    <t>ADWAITH ENDOTHERMIG</t>
+  </si>
+  <si>
+    <t>Beth sy'n digwydd i'r TYMHEREDD mewn adwaith ECSOTHERMIG?</t>
+  </si>
+  <si>
+    <t>Cynyddu</t>
+  </si>
+  <si>
+    <t>Beth sy'n digwydd i'r TYMHEREDD mewn adwaith ENDOTHERMIG?</t>
+  </si>
+  <si>
+    <t>Lleihau</t>
+  </si>
+  <si>
+    <t>Pa fath o adwaith yw hon?</t>
+  </si>
+  <si>
+    <t>Proffil Egni Ecsothermig.png</t>
+  </si>
+  <si>
+    <t>Proffil Egni Endothermig.png</t>
+  </si>
+  <si>
+    <t>Defnyddiwch y gwybodaeth i gyfrifo yr egni sydd ei angen i dorri'r bondiau yn yr hydrogen a clorin</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">H-H  =  436&lt;br&gt; Cl-Cl  =  243&lt;br&gt;&lt;br&gt;436 + 243 = </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="double"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>679kJ</t>
+    </r>
+  </si>
+  <si>
+    <t>Adwaith H2 a Cl2.png</t>
+  </si>
+  <si>
+    <t>Defnyddiwch y gwybodaeth i gyfrifo yr egni sydd yn cael ei ryddhau wrth ffurfio'r bondiau yn yr hydrogen clorid (HCl)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2 bond H-Cl =  432 x 2  =  864</t>
+    </r>
+    <r>
+      <rPr>
+        <u val="double"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>kJ</t>
+    </r>
+  </si>
+  <si>
+    <t>Dangoswch fod yr adwaith yn ecsothermig</t>
+  </si>
+  <si>
+    <t>egni    H-H   +   Cl-Cl  =   679kJ&lt;br&gt;&lt;br&gt; egni 2   x   H-Cl  =864kJ&lt;br&gt;&lt;br&gt; felly 679  -   864  =   -185kJ&lt;br&gt;&lt;br&gt;&lt;br&gt;Ateb yn negatif felly ECSOTHERMIG gan fod yr egni sy'n cael ei ryddhau yn fwy na'r egni sy'n cael ei amsugno.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -379,6 +671,13 @@
       <sz val="11"/>
       <name val="Aptos Narrow"/>
     </font>
+    <font>
+      <u val="double"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -407,13 +706,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -431,6 +725,18 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -653,518 +959,518 @@
   <dimension ref="A1:F45"/>
   <sheetFormatPr defaultColWidth="47" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="47" style="15"/>
-    <col min="2" max="2" width="47" style="14"/>
-    <col min="3" max="3" width="33.54296875" style="11" customWidth="1"/>
-    <col min="4" max="16384" width="47" style="11"/>
+    <col min="1" max="1" width="47" style="12"/>
+    <col min="2" max="2" width="47" style="11"/>
+    <col min="3" max="3" width="33.5703125" style="8" customWidth="1"/>
+    <col min="4" max="16384" width="47" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="7" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:6" s="4" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="12" t="s">
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="12" t="s">
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10" t="s">
+      <c r="C5" s="7"/>
+      <c r="D5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
     </row>
     <row r="6" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10" t="s">
+      <c r="C6" s="7"/>
+      <c r="D6" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
     </row>
     <row r="7" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
     </row>
     <row r="8" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
     </row>
     <row r="9" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
     </row>
     <row r="10" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+    </row>
+    <row r="11" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A11" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+    </row>
+    <row r="12" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+    </row>
+    <row r="13" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A13" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+    </row>
+    <row r="14" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A14" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+    </row>
+    <row r="15" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A15" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+    </row>
+    <row r="16" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A16" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+    </row>
+    <row r="17" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A17" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+    </row>
+    <row r="18" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A18" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+    </row>
+    <row r="19" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A19" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+    </row>
+    <row r="20" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A20" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A21" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+    </row>
+    <row r="22" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A22" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+    </row>
+    <row r="23" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A23" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+    </row>
+    <row r="24" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A24" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A25" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A26" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+    </row>
+    <row r="27" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A27" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+    </row>
+    <row r="28" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A28" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+    </row>
+    <row r="29" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A29" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A30" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+    </row>
+    <row r="31" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A31" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A32" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A33" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A34" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A35" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A36" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A37" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A38" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A39" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A40" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A41" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A42" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A43" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A44" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A45" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="B45" s="11" t="s">
         <v>94</v>
-      </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-    </row>
-    <row r="11" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A11" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-    </row>
-    <row r="12" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A12" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-    </row>
-    <row r="13" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A13" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-    </row>
-    <row r="14" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A14" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-    </row>
-    <row r="15" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A15" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-    </row>
-    <row r="16" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A16" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-    </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A17" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-    </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A18" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-    </row>
-    <row r="19" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A19" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-    </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A20" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-    </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A21" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-    </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A22" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-    </row>
-    <row r="23" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A23" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-    </row>
-    <row r="24" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A24" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-    </row>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A25" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-    </row>
-    <row r="26" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A26" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-    </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A27" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-    </row>
-    <row r="28" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A28" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-    </row>
-    <row r="29" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A29" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-    </row>
-    <row r="30" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A30" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-    </row>
-    <row r="31" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A31" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B31" s="14" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A32" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A33" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="B33" s="14" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A34" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A35" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="B35" s="14" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A36" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="B36" s="14" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A37" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="B37" s="14" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A38" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="B38" s="14" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A39" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="B39" s="14" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A40" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="B40" s="14" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A41" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="B41" s="14" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A42" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="B42" s="14" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A43" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="B43" s="14" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A44" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="B44" s="14" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A45" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="B45" s="14" t="s">
-        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1178,59 +1484,445 @@
   <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="12.75" customHeight="1"/>
   <cols>
-    <col min="1" max="4" width="49.453125" customWidth="1"/>
+    <col min="1" max="4" width="49.42578125" style="15" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="15"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
     </row>
     <row r="2" spans="1:6" ht="25.5" customHeight="1">
-      <c r="D2" s="1"/>
-    </row>
-    <row r="3" spans="1:6" ht="25.5" customHeight="1"/>
-    <row r="4" spans="1:6" ht="25.5" customHeight="1"/>
-    <row r="5" spans="1:6" ht="25.5" customHeight="1"/>
-    <row r="6" spans="1:6" ht="25.5" customHeight="1"/>
-    <row r="7" spans="1:6" ht="25.5" customHeight="1"/>
-    <row r="8" spans="1:6" ht="25.5" customHeight="1"/>
-    <row r="9" spans="1:6" ht="25.5" customHeight="1"/>
-    <row r="10" spans="1:6" ht="25.5" customHeight="1"/>
-    <row r="11" spans="1:6" ht="25.5" customHeight="1"/>
-    <row r="12" spans="1:6" ht="25.5" customHeight="1"/>
-    <row r="13" spans="1:6" ht="25.5" customHeight="1"/>
-    <row r="14" spans="1:6" ht="25.5" customHeight="1"/>
-    <row r="15" spans="1:6" ht="25.5" customHeight="1"/>
-    <row r="16" spans="1:6" ht="25.5" customHeight="1"/>
-    <row r="17" ht="25.5" customHeight="1"/>
-    <row r="18" ht="25.5" customHeight="1"/>
-    <row r="19" ht="25.5" customHeight="1"/>
-    <row r="20" ht="25.5" customHeight="1"/>
-    <row r="21" ht="25.5" customHeight="1"/>
-    <row r="22" ht="25.5" customHeight="1"/>
-    <row r="23" ht="25.5" customHeight="1"/>
-    <row r="24" ht="25.5" customHeight="1"/>
-    <row r="25" ht="25.5" customHeight="1"/>
-    <row r="26" ht="25.5" customHeight="1"/>
-    <row r="27" ht="25.5" customHeight="1"/>
-    <row r="28" ht="25.5" customHeight="1"/>
-    <row r="29" ht="25.5" customHeight="1"/>
-    <row r="30" ht="25.5" customHeight="1"/>
-    <row r="31" ht="25.5" customHeight="1"/>
-    <row r="32" ht="25.5" customHeight="1"/>
+      <c r="A2" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" s="16"/>
+    </row>
+    <row r="3" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A3" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A4" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A5" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A6" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A7" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A8" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A9" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A10" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A11" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A12" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A13" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A14" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A15" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A16" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="25.5" customHeight="1">
+      <c r="A17" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="25.5" customHeight="1">
+      <c r="A18" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="25.5" customHeight="1">
+      <c r="A19" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="25.5" customHeight="1">
+      <c r="A20" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="25.5" customHeight="1">
+      <c r="A21" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="25.5" customHeight="1">
+      <c r="A22" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="25.5" customHeight="1">
+      <c r="A23" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="25.5" customHeight="1">
+      <c r="A24" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="25.5" customHeight="1">
+      <c r="A25" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="25.5" customHeight="1">
+      <c r="A26" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="25.5" customHeight="1">
+      <c r="A27" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="25.5" customHeight="1">
+      <c r="A28" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="25.5" customHeight="1">
+      <c r="A29" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="25.5" customHeight="1">
+      <c r="A30" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="25.5" customHeight="1"/>
+    <row r="32" spans="1:3" ht="25.5" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3C1C183-043C-4181-ABFC-6CC837CF0487}">
+  <dimension ref="A1:F31"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="6" width="64.140625" style="14" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="28.5" customHeight="1">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+    </row>
+    <row r="2" spans="1:6" ht="27.75" customHeight="1">
+      <c r="A2" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="27.75" customHeight="1">
+      <c r="A3" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="27.75" customHeight="1">
+      <c r="A4" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="27.75" customHeight="1">
+      <c r="A5" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="27.75" customHeight="1">
+      <c r="A6" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="27.75" customHeight="1">
+      <c r="A7" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="27.75" customHeight="1">
+      <c r="A8" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="27.75" customHeight="1">
+      <c r="A9" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="27.75" customHeight="1">
+      <c r="A10" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="27.75" customHeight="1"/>
+    <row r="12" spans="1:6" ht="27.75" customHeight="1"/>
+    <row r="13" spans="1:6" ht="27.75" customHeight="1"/>
+    <row r="14" spans="1:6" ht="27.75" customHeight="1"/>
+    <row r="15" spans="1:6" ht="27.75" customHeight="1"/>
+    <row r="16" spans="1:6" ht="27.75" customHeight="1"/>
+    <row r="17" s="14" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="18" s="14" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="19" s="14" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="20" s="14" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="21" s="14" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="22" s="14" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="23" s="14" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="24" s="14" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="25" s="14" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="26" s="14" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="27" s="14" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="28" s="14" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="29" s="14" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="30" s="14" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="31" s="14" customFormat="1" ht="27.75" customHeight="1"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E57DDB98-DED6-44B3-9212-7621DBC6158B}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A7390D3-77B8-417A-BF28-251115C36B48}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1">
+        <v>5.4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1D33F75-CDBA-43E0-9D68-0D698FDC504D}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/CardiauFflachCemeg.xlsx
+++ b/CardiauFflachCemeg.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="381" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A527BE69-D69B-4138-9C53-B4E96BB5849D}"/>
+  <xr:revisionPtr revIDLastSave="389" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6381618F-DA8F-4B68-A4D7-C2E4BBE0955D}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="5.1 Bondio" sheetId="1" r:id="rId1"/>
     <sheet name="5.2 Asidau" sheetId="3" r:id="rId2"/>
-    <sheet name="5.3 Metelau (dim electrolysis)" sheetId="4" r:id="rId3"/>
+    <sheet name="5.3 Metelau (dim electrolysis)" sheetId="6" r:id="rId3"/>
     <sheet name="5.3 Metelau (electrolysis)" sheetId="5" r:id="rId4"/>
-    <sheet name="5.4 Egni" sheetId="6" r:id="rId5"/>
+    <sheet name="5.4 Egni." sheetId="4" r:id="rId5"/>
     <sheet name="5.5 Olew Crai" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="172">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -1757,6 +1757,54 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A7390D3-77B8-417A-BF28-251115C36B48}">
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="47.25">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E57DDB98-DED6-44B3-9212-7621DBC6158B}">
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="47.25">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3C1C183-043C-4181-ABFC-6CC837CF0487}">
   <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
@@ -1894,35 +1942,26 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E57DDB98-DED6-44B3-9212-7621DBC6158B}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A7390D3-77B8-417A-BF28-251115C36B48}">
-  <dimension ref="A1"/>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1D33F75-CDBA-43E0-9D68-0D698FDC504D}">
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1">
-        <v>5.4</v>
+    <row r="1" spans="1:4" ht="47.25">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1D33F75-CDBA-43E0-9D68-0D698FDC504D}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/CardiauFflachCemeg.xlsx
+++ b/CardiauFflachCemeg.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="389" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6381618F-DA8F-4B68-A4D7-C2E4BBE0955D}"/>
+  <xr:revisionPtr revIDLastSave="490" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1BED267-DD58-4A16-9ACE-E534662F4790}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="5.1 Bondio" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="240">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -614,6 +614,210 @@
   </si>
   <si>
     <t>egni    H-H   +   Cl-Cl  =   679kJ&lt;br&gt;&lt;br&gt; egni 2   x   H-Cl  =864kJ&lt;br&gt;&lt;br&gt; felly 679  -   864  =   -185kJ&lt;br&gt;&lt;br&gt;&lt;br&gt;Ateb yn negatif felly ECSOTHERMIG gan fod yr egni sy'n cael ei ryddhau yn fwy na'r egni sy'n cael ei amsugno.</t>
+  </si>
+  <si>
+    <t>Defnyddiwch yr ionau yma i roi fformiwla sodiwm ocsid&lt;br&gt;&lt;br&gt;$Na^+$   $O^2-$</t>
+  </si>
+  <si>
+    <t>$Na_2O$</t>
+  </si>
+  <si>
+    <t>Defnyddiwch yr ionau yma i roi fformiwla magnesiwm ocsid&lt;br&gt;&lt;br&gt;$Mg^2+$   $O^2-$</t>
+  </si>
+  <si>
+    <t>MgO</t>
+  </si>
+  <si>
+    <t>Beth yw enw'r math o adwaith pan fydd metel mwy adweithiol yn tynnu metel llai adweithiol o gyfansoddyn?</t>
+  </si>
+  <si>
+    <t>ADWAITH DADLEOLI</t>
+  </si>
+  <si>
+    <t>Beth yw'r enw ar restr o fetelau mewn trefn o'r mwyaf adweithiol i'r lleiaf adweithiol?</t>
+  </si>
+  <si>
+    <t>CYFRES ADWEITHEDD</t>
+  </si>
+  <si>
+    <t>Beth yw'r 4 deunydd crai sydd ei angen i echdynnu haearn o'i fwyn?</t>
+  </si>
+  <si>
+    <t>Mwyn haearn&lt;br&gt;&lt;br&gt;Golosg&lt;br&gt;&lt;br&gt;Aer poeth&lt;br&gt;&lt;br&gt;Calchfaen</t>
+  </si>
+  <si>
+    <t>Beth yw pwrpas rhoi mwyn haearn yn y Ffwrnais Chwyth?</t>
+  </si>
+  <si>
+    <t>Er mwyn cael ffynhonnell o haearn i'w echdynnu</t>
+  </si>
+  <si>
+    <t>Beth yw pwrpas rhoi golosg yn y Ffwrnais Chwyth?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fel tanwydd i gael gwres &lt;br&gt;&lt;br&gt;ac er mwyn cynhyrchu carbon monocsid i rydwytho'r haearn o'r mwyn haearn </t>
+  </si>
+  <si>
+    <t>Beth yw pwrpas rhoi aer poeth yn y Ffwrnais Chwyth?</t>
+  </si>
+  <si>
+    <t>Er mwyn cael ocsigen er mwyn i'r golosg losgi</t>
+  </si>
+  <si>
+    <t>Beth yw pwrpas rhoi calchfaen yn y Ffwrnais Chwyth?</t>
+  </si>
+  <si>
+    <t>Er mwyn cael gwared o amhureddau a ffurfio slag</t>
+  </si>
+  <si>
+    <t>Hafaliad echdynnu haearn.png</t>
+  </si>
+  <si>
+    <t>Beth sy'n cael ei RYDWYTHO? Rhowch eglurhad.</t>
+  </si>
+  <si>
+    <t>yr haearn ocsid gan ei fod yn COLLI OCSIGEN</t>
+  </si>
+  <si>
+    <t>Beth sy'n cael ei OCSIDIO? Rhowch eglurhad.</t>
+  </si>
+  <si>
+    <t>y carbon monocsid gan ei fod yn ENNILL OCSIGEN</t>
+  </si>
+  <si>
+    <t>Hafaliad Thermit.png</t>
+  </si>
+  <si>
+    <t>Beth yw enw'r adwaith ecsothermig iawn yma?</t>
+  </si>
+  <si>
+    <t>Adwaith THERMIT</t>
+  </si>
+  <si>
+    <t>RHYDWYTHIAD</t>
+  </si>
+  <si>
+    <t>Colli Ocsigen</t>
+  </si>
+  <si>
+    <t>OCSIDIAD</t>
+  </si>
+  <si>
+    <t>Ennill Ocsigen</t>
+  </si>
+  <si>
+    <t>Lliw cyfansoddion copr?</t>
+  </si>
+  <si>
+    <t>glas</t>
+  </si>
+  <si>
+    <t>Lliw cyfansoddion haearn(II)?</t>
+  </si>
+  <si>
+    <t>gwyrdd golau</t>
+  </si>
+  <si>
+    <t>Lliw cyfansoddion haearn(III)?</t>
+  </si>
+  <si>
+    <t>oren-brown</t>
+  </si>
+  <si>
+    <t>Priodwedd sy'n golygu taro metel yn siap gwahanol</t>
+  </si>
+  <si>
+    <t>hydrin</t>
+  </si>
+  <si>
+    <t>Gallu tynnu metel yn wifren</t>
+  </si>
+  <si>
+    <t>hydwyth</t>
+  </si>
+  <si>
+    <t>Priodweddau copr</t>
+  </si>
+  <si>
+    <t>dargludo gwres a trydan&lt;br&gt;gwrthgyrydol&lt;br&gt;hydrin a hydwyth&lt;br&gt;lliw deniadol(del)</t>
+  </si>
+  <si>
+    <t>Priodweddau alwminiwm</t>
+  </si>
+  <si>
+    <t>dargludo gwres a trydan&lt;br&gt;gwrthgyrydol&lt;br&gt;cryf&lt;br&gt;dwysedd isel</t>
+  </si>
+  <si>
+    <t>Priodweddau titaniwm</t>
+  </si>
+  <si>
+    <t>caled&lt;br&gt;cryf&lt;br&gt;gwrthgyrydol&lt;br&gt;ymdoddbwynt uchel&lt;br&gt;dwysedd isel</t>
+  </si>
+  <si>
+    <t>Priodweddau haearn</t>
+  </si>
+  <si>
+    <t>caled aa chryf</t>
+  </si>
+  <si>
+    <t>Beth yw aloi?</t>
+  </si>
+  <si>
+    <t>CYMYSGEDD o fetelau ac efallai carbon</t>
+  </si>
+  <si>
+    <t>Pam fod dur gwrthstaen yn cael ei ddefnyddio i wneud cyllyll a ffyrc?</t>
+  </si>
+  <si>
+    <t>gwrthgyrydol</t>
+  </si>
+  <si>
+    <t>Pam fod alwminiwm yn cael ei ddefnyddio i wneud ceblau trydan uwchben?</t>
+  </si>
+  <si>
+    <t>dargludo trydan a dwysedd isel</t>
+  </si>
+  <si>
+    <t>Pam fod titaniwm yn cael ei ddefnyddio i wneud clun a penglin newydd i gleifion?</t>
+  </si>
+  <si>
+    <t>cryf, gwrthgyrydol a dwysedd isel</t>
+  </si>
+  <si>
+    <t>Pam fod copr yn cael ei ddefnyddio i wneud pibellau dwr?</t>
+  </si>
+  <si>
+    <t>gwrthgyrydol a hydrin</t>
+  </si>
+  <si>
+    <t>Ffwrnais Chwyth.png</t>
+  </si>
+  <si>
+    <t>A&lt;br&gt;B&lt;br&gt;D</t>
+  </si>
+  <si>
+    <t>Fformiwla CaCO3.png</t>
+  </si>
+  <si>
+    <t>$CaCO_3$</t>
+  </si>
+  <si>
+    <t>Cydbwyso_1.png</t>
+  </si>
+  <si>
+    <t>Cyfrifo_Mr.png</t>
+  </si>
+  <si>
+    <t>40    +    28   +   16   +   16   +   16</t>
+  </si>
+  <si>
+    <t>Cydbwyso_2.png</t>
+  </si>
+  <si>
+    <t>Cydbwyso_3.png</t>
+  </si>
+  <si>
+    <t>3&lt;br&gt;&lt;br&gt;$AlCl_3$</t>
   </si>
 </sst>
 </file>
@@ -753,6 +957,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1749,8 +1957,22 @@
         <v>149</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="25.5" customHeight="1"/>
-    <row r="32" spans="1:3" ht="25.5" customHeight="1"/>
+    <row r="31" spans="1:3" ht="25.5" customHeight="1">
+      <c r="A31" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="25.5" customHeight="1">
+      <c r="A32" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>175</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1758,10 +1980,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A7390D3-77B8-417A-BF28-251115C36B48}">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="57.42578125" style="15" customWidth="1"/>
+    <col min="2" max="4" width="40.7109375" style="15" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="15"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="47.25">
+    <row r="1" spans="1:4" ht="29.25" customHeight="1">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -1773,6 +2000,271 @@
       </c>
       <c r="D1" s="13" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="29.25" customHeight="1">
+      <c r="A2" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="29.25" customHeight="1">
+      <c r="A3" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="29.25" customHeight="1">
+      <c r="A4" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="29.25" customHeight="1">
+      <c r="A5" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="29.25" customHeight="1">
+      <c r="A6" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="29.25" customHeight="1">
+      <c r="A7" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="29.25" customHeight="1">
+      <c r="A8" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="29.25" customHeight="1">
+      <c r="A9" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="29.25" customHeight="1">
+      <c r="A10" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="29.25" customHeight="1">
+      <c r="A11" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="29.25" customHeight="1">
+      <c r="A12" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="29.25" customHeight="1">
+      <c r="A13" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="29.25" customHeight="1">
+      <c r="A14" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="29.25" customHeight="1">
+      <c r="A15" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="29.25" customHeight="1">
+      <c r="A16" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="29.25" customHeight="1">
+      <c r="A17" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="29.25" customHeight="1">
+      <c r="A18" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="29.25" customHeight="1">
+      <c r="A19" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="29.25" customHeight="1">
+      <c r="A20" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="29.25" customHeight="1">
+      <c r="A21" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="29.25" customHeight="1">
+      <c r="A22" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="29.25" customHeight="1">
+      <c r="A23" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="29.25" customHeight="1">
+      <c r="A24" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="29.25" customHeight="1">
+      <c r="A25" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="29.25" customHeight="1">
+      <c r="A26" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="29.25" customHeight="1">
+      <c r="A27" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="29.25" customHeight="1">
+      <c r="B28" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="29.25" customHeight="1">
+      <c r="B29" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="B30" s="15">
+        <v>2</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="B31" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="B32" s="15">
+        <v>4</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3">
+      <c r="B33" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>238</v>
       </c>
     </row>
   </sheetData>

--- a/CardiauFflachCemeg.xlsx
+++ b/CardiauFflachCemeg.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30015"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="490" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1BED267-DD58-4A16-9ACE-E534662F4790}"/>
+  <xr:revisionPtr revIDLastSave="562" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A109D088-12E3-4A73-94B9-9E574F0930FC}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="5.1 Bondio" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="285">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -524,6 +524,345 @@
   </si>
   <si>
     <t>Rhoi 3 drop o'r DANGOSYDD yn yr alcali&lt;br&gt;Ychwanegu'r ASID o'r BWRED tan mae'r LLIW yn NEWID&lt;br&gt;GADAEL mewn lle CYNNES er mwyn i’r DŴR ANWEDDU</t>
+  </si>
+  <si>
+    <t>Defnyddiwch yr ionau yma i roi fformiwla sodiwm ocsid&lt;br&gt;&lt;br&gt;$Na^+$   $O^2-$</t>
+  </si>
+  <si>
+    <t>$Na_2O$</t>
+  </si>
+  <si>
+    <t>Defnyddiwch yr ionau yma i roi fformiwla magnesiwm ocsid&lt;br&gt;&lt;br&gt;$Mg^2+$   $O^2-$</t>
+  </si>
+  <si>
+    <t>MgO</t>
+  </si>
+  <si>
+    <t>Beth yw enw'r math o adwaith pan fydd metel mwy adweithiol yn tynnu metel llai adweithiol o gyfansoddyn?</t>
+  </si>
+  <si>
+    <t>ADWAITH DADLEOLI</t>
+  </si>
+  <si>
+    <t>Beth yw'r enw ar restr o fetelau mewn trefn o'r mwyaf adweithiol i'r lleiaf adweithiol?</t>
+  </si>
+  <si>
+    <t>CYFRES ADWEITHEDD</t>
+  </si>
+  <si>
+    <t>Beth yw'r 4 deunydd crai sydd ei angen i echdynnu haearn o'i fwyn?</t>
+  </si>
+  <si>
+    <t>Mwyn haearn&lt;br&gt;&lt;br&gt;Golosg&lt;br&gt;&lt;br&gt;Aer poeth&lt;br&gt;&lt;br&gt;Calchfaen</t>
+  </si>
+  <si>
+    <t>Beth yw pwrpas rhoi mwyn haearn yn y Ffwrnais Chwyth?</t>
+  </si>
+  <si>
+    <t>Er mwyn cael ffynhonnell o haearn i'w echdynnu</t>
+  </si>
+  <si>
+    <t>Beth yw pwrpas rhoi golosg yn y Ffwrnais Chwyth?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fel tanwydd i gael gwres &lt;br&gt;&lt;br&gt;ac er mwyn cynhyrchu carbon monocsid i rydwytho'r haearn o'r mwyn haearn </t>
+  </si>
+  <si>
+    <t>Beth yw pwrpas rhoi aer poeth yn y Ffwrnais Chwyth?</t>
+  </si>
+  <si>
+    <t>Er mwyn cael ocsigen er mwyn i'r golosg losgi</t>
+  </si>
+  <si>
+    <t>Beth yw pwrpas rhoi calchfaen yn y Ffwrnais Chwyth?</t>
+  </si>
+  <si>
+    <t>Er mwyn cael gwared o amhureddau a ffurfio slag</t>
+  </si>
+  <si>
+    <t>Beth sy'n cael ei RYDWYTHO? Rhowch eglurhad.</t>
+  </si>
+  <si>
+    <t>yr haearn ocsid gan ei fod yn COLLI OCSIGEN</t>
+  </si>
+  <si>
+    <t>Hafaliad echdynnu haearn.png</t>
+  </si>
+  <si>
+    <t>Beth sy'n cael ei OCSIDIO? Rhowch eglurhad.</t>
+  </si>
+  <si>
+    <t>y carbon monocsid gan ei fod yn ENNILL OCSIGEN</t>
+  </si>
+  <si>
+    <t>Beth yw enw'r adwaith ecsothermig iawn yma?</t>
+  </si>
+  <si>
+    <t>Adwaith THERMIT</t>
+  </si>
+  <si>
+    <t>Hafaliad Thermit.png</t>
+  </si>
+  <si>
+    <t>RHYDWYTHIAD</t>
+  </si>
+  <si>
+    <t>Colli Ocsigen</t>
+  </si>
+  <si>
+    <t>OCSIDIAD</t>
+  </si>
+  <si>
+    <t>Ennill Ocsigen</t>
+  </si>
+  <si>
+    <t>Lliw cyfansoddion copr?</t>
+  </si>
+  <si>
+    <t>glas</t>
+  </si>
+  <si>
+    <t>Lliw cyfansoddion haearn(II)?</t>
+  </si>
+  <si>
+    <t>gwyrdd golau</t>
+  </si>
+  <si>
+    <t>Lliw cyfansoddion haearn(III)?</t>
+  </si>
+  <si>
+    <t>oren-brown</t>
+  </si>
+  <si>
+    <t>Priodwedd sy'n golygu taro metel yn siap gwahanol</t>
+  </si>
+  <si>
+    <t>hydrin</t>
+  </si>
+  <si>
+    <t>Gallu tynnu metel yn wifren</t>
+  </si>
+  <si>
+    <t>hydwyth</t>
+  </si>
+  <si>
+    <t>Priodweddau copr</t>
+  </si>
+  <si>
+    <t>dargludo gwres a trydan&lt;br&gt;gwrthgyrydol&lt;br&gt;hydrin a hydwyth&lt;br&gt;lliw deniadol(del)</t>
+  </si>
+  <si>
+    <t>Priodweddau alwminiwm</t>
+  </si>
+  <si>
+    <t>dargludo gwres a trydan&lt;br&gt;gwrthgyrydol&lt;br&gt;cryf&lt;br&gt;dwysedd isel</t>
+  </si>
+  <si>
+    <t>Priodweddau titaniwm</t>
+  </si>
+  <si>
+    <t>caled&lt;br&gt;cryf&lt;br&gt;gwrthgyrydol&lt;br&gt;ymdoddbwynt uchel&lt;br&gt;dwysedd isel</t>
+  </si>
+  <si>
+    <t>Priodweddau haearn</t>
+  </si>
+  <si>
+    <t>caled aa chryf</t>
+  </si>
+  <si>
+    <t>Beth yw aloi?</t>
+  </si>
+  <si>
+    <t>CYMYSGEDD o fetelau ac efallai carbon</t>
+  </si>
+  <si>
+    <t>Pam fod dur gwrthstaen yn cael ei ddefnyddio i wneud cyllyll a ffyrc?</t>
+  </si>
+  <si>
+    <t>gwrthgyrydol</t>
+  </si>
+  <si>
+    <t>Pam fod alwminiwm yn cael ei ddefnyddio i wneud ceblau trydan uwchben?</t>
+  </si>
+  <si>
+    <t>dargludo trydan a dwysedd isel</t>
+  </si>
+  <si>
+    <t>Pam fod titaniwm yn cael ei ddefnyddio i wneud clun a penglin newydd i gleifion?</t>
+  </si>
+  <si>
+    <t>cryf, gwrthgyrydol a dwysedd isel</t>
+  </si>
+  <si>
+    <t>Pam fod copr yn cael ei ddefnyddio i wneud pibellau dwr?</t>
+  </si>
+  <si>
+    <t>gwrthgyrydol a hydrin</t>
+  </si>
+  <si>
+    <t>A&lt;br&gt;B&lt;br&gt;D</t>
+  </si>
+  <si>
+    <t>Ffwrnais Chwyth.png</t>
+  </si>
+  <si>
+    <t>$CaCO_3$</t>
+  </si>
+  <si>
+    <t>Fformiwla CaCO3.png</t>
+  </si>
+  <si>
+    <t>Cydbwyso_1.png</t>
+  </si>
+  <si>
+    <t>40    +    28   +   16   +   16   +   16</t>
+  </si>
+  <si>
+    <t>Cyfrifo_Mr.png</t>
+  </si>
+  <si>
+    <t>Cydbwyso_2.png</t>
+  </si>
+  <si>
+    <t>3&lt;br&gt;&lt;br&gt;$AlCl_3$</t>
+  </si>
+  <si>
+    <t>Cydbwyso_3.png</t>
+  </si>
+  <si>
+    <t>Electrolysis</t>
+  </si>
+  <si>
+    <t>defnyddio trydan i dorri cyfansoddyn ionig</t>
+  </si>
+  <si>
+    <t>Electrolyt</t>
+  </si>
+  <si>
+    <t>hylif sy’n cael ei dorri trwy electrolysis</t>
+  </si>
+  <si>
+    <t>Electrod</t>
+  </si>
+  <si>
+    <t>rhoden carbon sy’n cael ei roi mewn electrolyt </t>
+  </si>
+  <si>
+    <t>Catod</t>
+  </si>
+  <si>
+    <t>electrod negatif</t>
+  </si>
+  <si>
+    <t>Anod</t>
+  </si>
+  <si>
+    <t>electrod positif</t>
+  </si>
+  <si>
+    <t>Rhydwythiad</t>
+  </si>
+  <si>
+    <t>ennill electronau (REE)</t>
+  </si>
+  <si>
+    <t>Ocsidiad</t>
+  </si>
+  <si>
+    <t>colli electronau (OCE)</t>
+  </si>
+  <si>
+    <t>"-"</t>
+  </si>
+  <si>
+    <t>GWEFR negatif</t>
+  </si>
+  <si>
+    <t>"+"</t>
+  </si>
+  <si>
+    <t>GWEFR positif</t>
+  </si>
+  <si>
+    <t>Mwyn alwminiwm</t>
+  </si>
+  <si>
+    <t>Bocsit</t>
+  </si>
+  <si>
+    <t>Cyfansoddyn alwminiwm sydd mewn bocsit</t>
+  </si>
+  <si>
+    <t>alwminiwm ocsid (Alwmina)</t>
+  </si>
+  <si>
+    <t>Beth yw A?</t>
+  </si>
+  <si>
+    <t>Swigod o nwy ocsigen</t>
+  </si>
+  <si>
+    <t>Electrolysis_Al2O3.png</t>
+  </si>
+  <si>
+    <t>Beth yw B?</t>
+  </si>
+  <si>
+    <t>Anod graffit (electrod positif)</t>
+  </si>
+  <si>
+    <t>Beth yw C?</t>
+  </si>
+  <si>
+    <t>Catod graffit (electrod negatif)</t>
+  </si>
+  <si>
+    <t>Beth yw Ch?</t>
+  </si>
+  <si>
+    <t>Alwminiwm tawdd (wdi ei ymdoddi yn hylif)</t>
+  </si>
+  <si>
+    <t>Beth yw D?</t>
+  </si>
+  <si>
+    <t>Yr Electrolyt - alwminiwm ocsid (Alwmina)</t>
+  </si>
+  <si>
+    <t>Beth sydd wedi digwydd i'r alwminiwm?</t>
+  </si>
+  <si>
+    <t>RHYDWYTHO</t>
+  </si>
+  <si>
+    <t>Hafaliad_rhydwythiad_ionau_Al.png</t>
+  </si>
+  <si>
+    <t>Enw'r electrolyt?</t>
+  </si>
+  <si>
+    <t>copr(II) clorid</t>
+  </si>
+  <si>
+    <t>Electrolysis_CuCl2.png</t>
+  </si>
+  <si>
+    <t>Enw'r electrod negatif?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">catod  </t>
+  </si>
+  <si>
+    <t>Fformiwla copr(II) clorid</t>
+  </si>
+  <si>
+    <t>$CuCl_2$</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>Hafaliad_rhydwytho_Cu</t>
   </si>
   <si>
     <t>Pa fath o adwaith sy'n RHYDDHAU EGNI?</t>
@@ -615,216 +954,12 @@
   <si>
     <t>egni    H-H   +   Cl-Cl  =   679kJ&lt;br&gt;&lt;br&gt; egni 2   x   H-Cl  =864kJ&lt;br&gt;&lt;br&gt; felly 679  -   864  =   -185kJ&lt;br&gt;&lt;br&gt;&lt;br&gt;Ateb yn negatif felly ECSOTHERMIG gan fod yr egni sy'n cael ei ryddhau yn fwy na'r egni sy'n cael ei amsugno.</t>
   </si>
-  <si>
-    <t>Defnyddiwch yr ionau yma i roi fformiwla sodiwm ocsid&lt;br&gt;&lt;br&gt;$Na^+$   $O^2-$</t>
-  </si>
-  <si>
-    <t>$Na_2O$</t>
-  </si>
-  <si>
-    <t>Defnyddiwch yr ionau yma i roi fformiwla magnesiwm ocsid&lt;br&gt;&lt;br&gt;$Mg^2+$   $O^2-$</t>
-  </si>
-  <si>
-    <t>MgO</t>
-  </si>
-  <si>
-    <t>Beth yw enw'r math o adwaith pan fydd metel mwy adweithiol yn tynnu metel llai adweithiol o gyfansoddyn?</t>
-  </si>
-  <si>
-    <t>ADWAITH DADLEOLI</t>
-  </si>
-  <si>
-    <t>Beth yw'r enw ar restr o fetelau mewn trefn o'r mwyaf adweithiol i'r lleiaf adweithiol?</t>
-  </si>
-  <si>
-    <t>CYFRES ADWEITHEDD</t>
-  </si>
-  <si>
-    <t>Beth yw'r 4 deunydd crai sydd ei angen i echdynnu haearn o'i fwyn?</t>
-  </si>
-  <si>
-    <t>Mwyn haearn&lt;br&gt;&lt;br&gt;Golosg&lt;br&gt;&lt;br&gt;Aer poeth&lt;br&gt;&lt;br&gt;Calchfaen</t>
-  </si>
-  <si>
-    <t>Beth yw pwrpas rhoi mwyn haearn yn y Ffwrnais Chwyth?</t>
-  </si>
-  <si>
-    <t>Er mwyn cael ffynhonnell o haearn i'w echdynnu</t>
-  </si>
-  <si>
-    <t>Beth yw pwrpas rhoi golosg yn y Ffwrnais Chwyth?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fel tanwydd i gael gwres &lt;br&gt;&lt;br&gt;ac er mwyn cynhyrchu carbon monocsid i rydwytho'r haearn o'r mwyn haearn </t>
-  </si>
-  <si>
-    <t>Beth yw pwrpas rhoi aer poeth yn y Ffwrnais Chwyth?</t>
-  </si>
-  <si>
-    <t>Er mwyn cael ocsigen er mwyn i'r golosg losgi</t>
-  </si>
-  <si>
-    <t>Beth yw pwrpas rhoi calchfaen yn y Ffwrnais Chwyth?</t>
-  </si>
-  <si>
-    <t>Er mwyn cael gwared o amhureddau a ffurfio slag</t>
-  </si>
-  <si>
-    <t>Hafaliad echdynnu haearn.png</t>
-  </si>
-  <si>
-    <t>Beth sy'n cael ei RYDWYTHO? Rhowch eglurhad.</t>
-  </si>
-  <si>
-    <t>yr haearn ocsid gan ei fod yn COLLI OCSIGEN</t>
-  </si>
-  <si>
-    <t>Beth sy'n cael ei OCSIDIO? Rhowch eglurhad.</t>
-  </si>
-  <si>
-    <t>y carbon monocsid gan ei fod yn ENNILL OCSIGEN</t>
-  </si>
-  <si>
-    <t>Hafaliad Thermit.png</t>
-  </si>
-  <si>
-    <t>Beth yw enw'r adwaith ecsothermig iawn yma?</t>
-  </si>
-  <si>
-    <t>Adwaith THERMIT</t>
-  </si>
-  <si>
-    <t>RHYDWYTHIAD</t>
-  </si>
-  <si>
-    <t>Colli Ocsigen</t>
-  </si>
-  <si>
-    <t>OCSIDIAD</t>
-  </si>
-  <si>
-    <t>Ennill Ocsigen</t>
-  </si>
-  <si>
-    <t>Lliw cyfansoddion copr?</t>
-  </si>
-  <si>
-    <t>glas</t>
-  </si>
-  <si>
-    <t>Lliw cyfansoddion haearn(II)?</t>
-  </si>
-  <si>
-    <t>gwyrdd golau</t>
-  </si>
-  <si>
-    <t>Lliw cyfansoddion haearn(III)?</t>
-  </si>
-  <si>
-    <t>oren-brown</t>
-  </si>
-  <si>
-    <t>Priodwedd sy'n golygu taro metel yn siap gwahanol</t>
-  </si>
-  <si>
-    <t>hydrin</t>
-  </si>
-  <si>
-    <t>Gallu tynnu metel yn wifren</t>
-  </si>
-  <si>
-    <t>hydwyth</t>
-  </si>
-  <si>
-    <t>Priodweddau copr</t>
-  </si>
-  <si>
-    <t>dargludo gwres a trydan&lt;br&gt;gwrthgyrydol&lt;br&gt;hydrin a hydwyth&lt;br&gt;lliw deniadol(del)</t>
-  </si>
-  <si>
-    <t>Priodweddau alwminiwm</t>
-  </si>
-  <si>
-    <t>dargludo gwres a trydan&lt;br&gt;gwrthgyrydol&lt;br&gt;cryf&lt;br&gt;dwysedd isel</t>
-  </si>
-  <si>
-    <t>Priodweddau titaniwm</t>
-  </si>
-  <si>
-    <t>caled&lt;br&gt;cryf&lt;br&gt;gwrthgyrydol&lt;br&gt;ymdoddbwynt uchel&lt;br&gt;dwysedd isel</t>
-  </si>
-  <si>
-    <t>Priodweddau haearn</t>
-  </si>
-  <si>
-    <t>caled aa chryf</t>
-  </si>
-  <si>
-    <t>Beth yw aloi?</t>
-  </si>
-  <si>
-    <t>CYMYSGEDD o fetelau ac efallai carbon</t>
-  </si>
-  <si>
-    <t>Pam fod dur gwrthstaen yn cael ei ddefnyddio i wneud cyllyll a ffyrc?</t>
-  </si>
-  <si>
-    <t>gwrthgyrydol</t>
-  </si>
-  <si>
-    <t>Pam fod alwminiwm yn cael ei ddefnyddio i wneud ceblau trydan uwchben?</t>
-  </si>
-  <si>
-    <t>dargludo trydan a dwysedd isel</t>
-  </si>
-  <si>
-    <t>Pam fod titaniwm yn cael ei ddefnyddio i wneud clun a penglin newydd i gleifion?</t>
-  </si>
-  <si>
-    <t>cryf, gwrthgyrydol a dwysedd isel</t>
-  </si>
-  <si>
-    <t>Pam fod copr yn cael ei ddefnyddio i wneud pibellau dwr?</t>
-  </si>
-  <si>
-    <t>gwrthgyrydol a hydrin</t>
-  </si>
-  <si>
-    <t>Ffwrnais Chwyth.png</t>
-  </si>
-  <si>
-    <t>A&lt;br&gt;B&lt;br&gt;D</t>
-  </si>
-  <si>
-    <t>Fformiwla CaCO3.png</t>
-  </si>
-  <si>
-    <t>$CaCO_3$</t>
-  </si>
-  <si>
-    <t>Cydbwyso_1.png</t>
-  </si>
-  <si>
-    <t>Cyfrifo_Mr.png</t>
-  </si>
-  <si>
-    <t>40    +    28   +   16   +   16   +   16</t>
-  </si>
-  <si>
-    <t>Cydbwyso_2.png</t>
-  </si>
-  <si>
-    <t>Cydbwyso_3.png</t>
-  </si>
-  <si>
-    <t>3&lt;br&gt;&lt;br&gt;$AlCl_3$</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -882,6 +1017,13 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -910,7 +1052,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -942,6 +1084,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -957,10 +1103,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1959,18 +2101,18 @@
     </row>
     <row r="31" spans="1:3" ht="25.5" customHeight="1">
       <c r="A31" s="15" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="25.5" customHeight="1">
       <c r="A32" s="15" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -2004,235 +2146,235 @@
     </row>
     <row r="2" spans="1:4" ht="29.25" customHeight="1">
       <c r="A2" s="15" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="29.25" customHeight="1">
       <c r="A3" s="15" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="29.25" customHeight="1">
       <c r="A4" s="15" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="29.25" customHeight="1">
       <c r="A5" s="15" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="29.25" customHeight="1">
       <c r="A6" s="15" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="29.25" customHeight="1">
       <c r="A7" s="15" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="29.25" customHeight="1">
       <c r="A8" s="15" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="29.25" customHeight="1">
       <c r="A9" s="15" t="s">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="29.25" customHeight="1">
       <c r="A10" s="15" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="29.25" customHeight="1">
       <c r="A11" s="15" t="s">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>197</v>
+        <v>178</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="29.25" customHeight="1">
       <c r="A12" s="15" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="29.25" customHeight="1">
       <c r="A13" s="15" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="29.25" customHeight="1">
       <c r="A14" s="15" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="29.25" customHeight="1">
       <c r="A15" s="15" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="29.25" customHeight="1">
       <c r="A16" s="15" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="29.25" customHeight="1">
       <c r="A17" s="15" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="29.25" customHeight="1">
       <c r="A18" s="15" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="29.25" customHeight="1">
       <c r="A19" s="15" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="29.25" customHeight="1">
       <c r="A20" s="15" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="29.25" customHeight="1">
       <c r="A21" s="15" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="29.25" customHeight="1">
       <c r="A22" s="15" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="29.25" customHeight="1">
       <c r="A23" s="15" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="29.25" customHeight="1">
       <c r="A24" s="15" t="s">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="29.25" customHeight="1">
       <c r="A25" s="15" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="29.25" customHeight="1">
       <c r="A26" s="15" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="29.25" customHeight="1">
       <c r="A27" s="15" t="s">
-        <v>228</v>
+        <v>210</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="29.25" customHeight="1">
       <c r="B28" s="15" t="s">
-        <v>231</v>
+        <v>212</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="29.25" customHeight="1">
       <c r="B29" s="15" t="s">
-        <v>233</v>
+        <v>214</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -2240,15 +2382,15 @@
         <v>2</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>234</v>
+        <v>216</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="B31" s="15" t="s">
-        <v>236</v>
+        <v>217</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -2256,15 +2398,15 @@
         <v>4</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
     </row>
     <row r="33" spans="2:3">
       <c r="B33" s="15" t="s">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -2274,23 +2416,234 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E57DDB98-DED6-44B3-9212-7621DBC6158B}">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="51.85546875" customWidth="1"/>
+    <col min="2" max="2" width="51" customWidth="1"/>
+    <col min="3" max="4" width="27" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="47.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:4" s="18" customFormat="1" ht="30.75" customHeight="1">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="17" t="s">
         <v>3</v>
       </c>
     </row>
+    <row r="2" spans="1:4" s="18" customFormat="1">
+      <c r="A2" s="18" t="s">
+        <v>222</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" s="18" customFormat="1">
+      <c r="A3" s="18" t="s">
+        <v>224</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" s="18" customFormat="1">
+      <c r="A4" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" s="18" customFormat="1">
+      <c r="A5" s="18" t="s">
+        <v>228</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" s="18" customFormat="1">
+      <c r="A6" s="18" t="s">
+        <v>230</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" s="18" customFormat="1">
+      <c r="A7" s="18" t="s">
+        <v>232</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" s="18" customFormat="1">
+      <c r="A8" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" s="18" customFormat="1">
+      <c r="A9" s="18" t="s">
+        <v>236</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" s="18" customFormat="1">
+      <c r="A10" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" s="18" customFormat="1">
+      <c r="A11" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" s="18" customFormat="1">
+      <c r="A12" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" s="18" customFormat="1">
+      <c r="A13" s="18" t="s">
+        <v>244</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" s="18" customFormat="1">
+      <c r="A14" s="18" t="s">
+        <v>247</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>248</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" s="18" customFormat="1">
+      <c r="A15" s="18" t="s">
+        <v>249</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>250</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" s="18" customFormat="1">
+      <c r="A16" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>252</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" s="18" customFormat="1">
+      <c r="A17" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" s="18" customFormat="1">
+      <c r="A18" s="18" t="s">
+        <v>255</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>256</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" s="18" customFormat="1">
+      <c r="A19" s="18" t="s">
+        <v>258</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>259</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" s="18" customFormat="1">
+      <c r="A20" s="18" t="s">
+        <v>261</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" s="18" customFormat="1">
+      <c r="A21" s="18" t="s">
+        <v>263</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>264</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" s="18" customFormat="1">
+      <c r="B22" s="18" t="s">
+        <v>265</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" s="18" customFormat="1"/>
+    <row r="24" spans="1:3" s="18" customFormat="1"/>
+    <row r="25" spans="1:3" s="18" customFormat="1"/>
+    <row r="26" spans="1:3" s="18" customFormat="1"/>
+    <row r="27" spans="1:3" s="18" customFormat="1"/>
+    <row r="28" spans="1:3" s="18" customFormat="1"/>
+    <row r="29" spans="1:3" s="18" customFormat="1"/>
+    <row r="30" spans="1:3" s="18" customFormat="1"/>
+    <row r="31" spans="1:3" s="18" customFormat="1"/>
+    <row r="32" spans="1:3" s="18" customFormat="1"/>
+    <row r="33" s="18" customFormat="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2323,89 +2676,89 @@
     </row>
     <row r="2" spans="1:6" ht="27.75" customHeight="1">
       <c r="A2" s="14" t="s">
-        <v>154</v>
+        <v>267</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>155</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="27.75" customHeight="1">
       <c r="A3" s="14" t="s">
-        <v>156</v>
+        <v>269</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>157</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="27.75" customHeight="1">
       <c r="A4" s="14" t="s">
-        <v>158</v>
+        <v>271</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>159</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1">
       <c r="A5" s="14" t="s">
-        <v>160</v>
+        <v>273</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>161</v>
+        <v>274</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="27.75" customHeight="1">
       <c r="A6" s="14" t="s">
-        <v>162</v>
+        <v>275</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>155</v>
+        <v>268</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>163</v>
+        <v>276</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="27.75" customHeight="1">
       <c r="A7" s="14" t="s">
-        <v>162</v>
+        <v>275</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>157</v>
+        <v>270</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>164</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="27.75" customHeight="1">
       <c r="A8" s="15" t="s">
-        <v>165</v>
+        <v>278</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>166</v>
+        <v>279</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>167</v>
+        <v>280</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="27.75" customHeight="1">
       <c r="A9" s="15" t="s">
-        <v>168</v>
+        <v>281</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>169</v>
+        <v>282</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>167</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="27.75" customHeight="1">
       <c r="A10" s="15" t="s">
-        <v>170</v>
+        <v>283</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>171</v>
+        <v>284</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>167</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="27.75" customHeight="1"/>

--- a/CardiauFflachCemeg.xlsx
+++ b/CardiauFflachCemeg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="562" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A109D088-12E3-4A73-94B9-9E574F0930FC}"/>
+  <xr:revisionPtr revIDLastSave="563" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8255E47A-27FB-4CF3-880A-44FC9C2770AC}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -862,7 +862,7 @@
     <t>C</t>
   </si>
   <si>
-    <t>Hafaliad_rhydwytho_Cu</t>
+    <t>Hafaliad_rhydwytho_Cu.png</t>
   </si>
   <si>
     <t>Pa fath o adwaith sy'n RHYDDHAU EGNI?</t>
@@ -1052,7 +1052,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1087,7 +1087,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2424,7 +2423,7 @@
     <col min="3" max="4" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="18" customFormat="1" ht="30.75" customHeight="1">
+    <row r="1" spans="1:4" ht="30.75" customHeight="1">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -2438,212 +2437,202 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="18" customFormat="1">
-      <c r="A2" s="18" t="s">
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
         <v>222</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="18" customFormat="1">
-      <c r="A3" s="18" t="s">
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
         <v>224</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="18" customFormat="1">
-      <c r="A4" s="18" t="s">
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
         <v>226</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="5" spans="1:4" s="18" customFormat="1">
-      <c r="A5" s="18" t="s">
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
         <v>228</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="6" spans="1:4" s="18" customFormat="1">
-      <c r="A6" s="18" t="s">
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
         <v>230</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="7" spans="1:4" s="18" customFormat="1">
-      <c r="A7" s="18" t="s">
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
         <v>232</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="8" spans="1:4" s="18" customFormat="1">
-      <c r="A8" s="18" t="s">
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
         <v>234</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="9" spans="1:4" s="18" customFormat="1">
-      <c r="A9" s="18" t="s">
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
         <v>236</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="10" spans="1:4" s="18" customFormat="1">
-      <c r="A10" s="18" t="s">
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
         <v>238</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="11" spans="1:4" s="18" customFormat="1">
-      <c r="A11" s="18" t="s">
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
         <v>240</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="12" spans="1:4" s="18" customFormat="1">
-      <c r="A12" s="18" t="s">
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
         <v>242</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="13" spans="1:4" s="18" customFormat="1">
-      <c r="A13" s="18" t="s">
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
         <v>244</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" t="s">
         <v>245</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="14" spans="1:4" s="18" customFormat="1">
-      <c r="A14" s="18" t="s">
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
         <v>247</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" t="s">
         <v>248</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="15" spans="1:4" s="18" customFormat="1">
-      <c r="A15" s="18" t="s">
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
         <v>249</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B15" t="s">
         <v>250</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="16" spans="1:4" s="18" customFormat="1">
-      <c r="A16" s="18" t="s">
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
         <v>251</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" t="s">
         <v>252</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="17" spans="1:3" s="18" customFormat="1">
-      <c r="A17" s="18" t="s">
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
         <v>253</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B17" t="s">
         <v>254</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="18" spans="1:3" s="18" customFormat="1">
-      <c r="A18" s="18" t="s">
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
         <v>255</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" t="s">
         <v>256</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="18" customFormat="1">
-      <c r="A19" s="18" t="s">
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
         <v>258</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="B19" t="s">
         <v>259</v>
       </c>
-      <c r="C19" s="18" t="s">
+      <c r="C19" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="18" customFormat="1">
-      <c r="A20" s="18" t="s">
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
         <v>261</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B20" t="s">
         <v>262</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="18" customFormat="1">
-      <c r="A21" s="18" t="s">
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
         <v>263</v>
       </c>
-      <c r="B21" s="18" t="s">
+      <c r="B21" t="s">
         <v>264</v>
       </c>
-      <c r="C21" s="18" t="s">
+      <c r="C21" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="22" spans="1:3" s="18" customFormat="1">
-      <c r="B22" s="18" t="s">
+    <row r="22" spans="1:3">
+      <c r="B22" t="s">
         <v>265</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="23" spans="1:3" s="18" customFormat="1"/>
-    <row r="24" spans="1:3" s="18" customFormat="1"/>
-    <row r="25" spans="1:3" s="18" customFormat="1"/>
-    <row r="26" spans="1:3" s="18" customFormat="1"/>
-    <row r="27" spans="1:3" s="18" customFormat="1"/>
-    <row r="28" spans="1:3" s="18" customFormat="1"/>
-    <row r="29" spans="1:3" s="18" customFormat="1"/>
-    <row r="30" spans="1:3" s="18" customFormat="1"/>
-    <row r="31" spans="1:3" s="18" customFormat="1"/>
-    <row r="32" spans="1:3" s="18" customFormat="1"/>
-    <row r="33" s="18" customFormat="1"/>
+    <row r="33" customFormat="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/CardiauFflachCemeg.xlsx
+++ b/CardiauFflachCemeg.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30015"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="563" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8255E47A-27FB-4CF3-880A-44FC9C2770AC}"/>
+  <xr:revisionPtr revIDLastSave="568" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CDCD38E3-E88B-4996-80F7-EB9DEA83EC1D}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-720" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="5.1 Bondio" sheetId="1" r:id="rId1"/>
@@ -859,9 +859,6 @@
     <t>$CuCl_2$</t>
   </si>
   <si>
-    <t>C</t>
-  </si>
-  <si>
     <t>Hafaliad_rhydwytho_Cu.png</t>
   </si>
   <si>
@@ -953,6 +950,9 @@
   </si>
   <si>
     <t>egni    H-H   +   Cl-Cl  =   679kJ&lt;br&gt;&lt;br&gt; egni 2   x   H-Cl  =864kJ&lt;br&gt;&lt;br&gt; felly 679  -   864  =   -185kJ&lt;br&gt;&lt;br&gt;&lt;br&gt;Ateb yn negatif felly ECSOTHERMIG gan fod yr egni sy'n cael ei ryddhau yn fwy na'r egni sy'n cael ei amsugno.</t>
+  </si>
+  <si>
+    <t>???????</t>
   </si>
 </sst>
 </file>
@@ -1102,6 +1102,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2626,10 +2630,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="B22" t="s">
+        <v>284</v>
+      </c>
+      <c r="C22" t="s">
         <v>265</v>
-      </c>
-      <c r="C22" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="33" customFormat="1"/>
@@ -2665,89 +2669,89 @@
     </row>
     <row r="2" spans="1:6" ht="27.75" customHeight="1">
       <c r="A2" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="B2" s="14" t="s">
         <v>267</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="27.75" customHeight="1">
       <c r="A3" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="B3" s="14" t="s">
         <v>269</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="27.75" customHeight="1">
       <c r="A4" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="B4" s="14" t="s">
         <v>271</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1">
       <c r="A5" s="14" t="s">
+        <v>272</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>273</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="27.75" customHeight="1">
       <c r="A6" s="14" t="s">
+        <v>274</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="C6" s="14" t="s">
         <v>275</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>268</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="27.75" customHeight="1">
       <c r="A7" s="14" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="27.75" customHeight="1">
       <c r="A8" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="B8" s="14" t="s">
         <v>278</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="C8" s="14" t="s">
         <v>279</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="27.75" customHeight="1">
       <c r="A9" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="B9" s="14" t="s">
         <v>281</v>
       </c>
-      <c r="B9" s="14" t="s">
-        <v>282</v>
-      </c>
       <c r="C9" s="14" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="27.75" customHeight="1">
       <c r="A10" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="B10" s="14" t="s">
         <v>283</v>
       </c>
-      <c r="B10" s="14" t="s">
-        <v>284</v>
-      </c>
       <c r="C10" s="14" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="27.75" customHeight="1"/>

--- a/CardiauFflachCemeg.xlsx
+++ b/CardiauFflachCemeg.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30015"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="568" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CDCD38E3-E88B-4996-80F7-EB9DEA83EC1D}"/>
+  <xr:revisionPtr revIDLastSave="683" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B622F70-E00C-4A42-8A71-CB7B468FD8DB}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-720" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="5.1 Bondio" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="342">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -857,6 +857,12 @@
   </si>
   <si>
     <t>$CuCl_2$</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>C</t>
   </si>
   <si>
     <t>Hafaliad_rhydwytho_Cu.png</t>
@@ -952,14 +958,179 @@
     <t>egni    H-H   +   Cl-Cl  =   679kJ&lt;br&gt;&lt;br&gt; egni 2   x   H-Cl  =864kJ&lt;br&gt;&lt;br&gt; felly 679  -   864  =   -185kJ&lt;br&gt;&lt;br&gt;&lt;br&gt;Ateb yn negatif felly ECSOTHERMIG gan fod yr egni sy'n cael ei ryddhau yn fwy na'r egni sy'n cael ei amsugno.</t>
   </si>
   <si>
-    <t>???????</t>
+    <t>Sut cafodd olew crai ei ffurfio?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O weddillion organebau MOROL&lt;br&gt;Gwres a gwasgedd&lt;br&gt;Dros filiynau o flynyddoedd </t>
+  </si>
+  <si>
+    <t>Beth yw Anadnewyddadwy?</t>
+  </si>
+  <si>
+    <t>bydd yn rhedeg allan / ni fydd yn parhau am byth</t>
+  </si>
+  <si>
+    <t>Beth yw enw'r broses o wahanu'r ffracsiynau gwahanol mewn olew crai?</t>
+  </si>
+  <si>
+    <t>DISTYLLIAD FFRACSIYNOL</t>
+  </si>
+  <si>
+    <t>Pam fod fy fracsiynau gwahanol  mewn olew crai yn gallu cael eu gwahanu trwy ddistylliad ffracsiynol?</t>
+  </si>
+  <si>
+    <t>BERWBWYNT GWAHANOL ganddynt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y mwyaf yw maint y moleciwl yr ________________ yw berwbwynt. </t>
+  </si>
+  <si>
+    <t>UCHAF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y mwyaf yw maint y moleciwl y ________________tywyll yw ei liw. </t>
+  </si>
+  <si>
+    <t>MWYAF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y mwyaf yw maint y moleciwl yr ________________ yw ei danio. </t>
+  </si>
+  <si>
+    <t>ANODDAF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y mwyaf yw maint y moleciwl y ________________  trwchus yw'r hylif. </t>
+  </si>
+  <si>
+    <t>Beth yw HYDROCARBONAU?</t>
+  </si>
+  <si>
+    <t>Cyfansoddion o CARBON a HYDROGEN</t>
+  </si>
+  <si>
+    <t>Cynhyrchion HYLOSGIAD hydrocarbonau?</t>
+  </si>
+  <si>
+    <t>Carbon deuocsid a dŵr</t>
+  </si>
+  <si>
+    <t>Pa hydrocarbonau sydd â bond dwbl C=C?</t>
+  </si>
+  <si>
+    <t>ALCENAU</t>
+  </si>
+  <si>
+    <t>Pa hydrocarbonau sydd DDIM yn cynnwys bond dwbl C=C?</t>
+  </si>
+  <si>
+    <t>ALCANAU</t>
+  </si>
+  <si>
+    <t>Pa hydrocarbonau sydd â'r formiwla cyffredinol $C_nH_2n+2$?</t>
+  </si>
+  <si>
+    <t>Pa hydrocarbonau sydd â'r formiwla cyffredinol $C_nH_2n$?</t>
+  </si>
+  <si>
+    <t>Pa hydrocarbonau sydd yn ANNIRLAWN?</t>
+  </si>
+  <si>
+    <t>Pa hydrocarbonau sydd yn DDIRLAWN?</t>
+  </si>
+  <si>
+    <t>Cynhyrchion hylosgiad methan?</t>
+  </si>
+  <si>
+    <t>Enw $C_2H_6$?</t>
+  </si>
+  <si>
+    <t>Ethan</t>
+  </si>
+  <si>
+    <t>Enw $C_3H_6$?</t>
+  </si>
+  <si>
+    <t>Propen</t>
+  </si>
+  <si>
+    <t>Arsylwadau adwaith rhwng alcen a bromin?</t>
+  </si>
+  <si>
+    <t>Newid lliw o oren-frown i di-liw</t>
+  </si>
+  <si>
+    <t>Prawf am bond dwbl C=C?</t>
+  </si>
+  <si>
+    <t>Ychwanegu bromin fydd yn newid lliw o oren-frown i di-liw</t>
+  </si>
+  <si>
+    <t>Enw'r polymer sy'n ffurfio o ethen?</t>
+  </si>
+  <si>
+    <t>Polyethen</t>
+  </si>
+  <si>
+    <t>Enw'r polymer sy'n ffurfio o propen?</t>
+  </si>
+  <si>
+    <t>Polypropen</t>
+  </si>
+  <si>
+    <t>Enw'r polymer sy'n ffurfio o finylclorid?</t>
+  </si>
+  <si>
+    <t>Polyfinylclorid (PVC)</t>
+  </si>
+  <si>
+    <t>Enw'r polymer sy'n ffurfio o tetrafflworoethen?</t>
+  </si>
+  <si>
+    <t>Polytetrafflworoethen (PTFE)</t>
+  </si>
+  <si>
+    <t>CRACIO hydrocarbonau?</t>
+  </si>
+  <si>
+    <t>Torri hydrocarbonau mawr yn rai llai trwy eu gwresogi gyda chatalydd</t>
+  </si>
+  <si>
+    <t>Priodweddau Polymerau (plastigion)?</t>
+  </si>
+  <si>
+    <t>Ynysydd trydanol a thermol&lt;br&gt;&lt;br&gt;Cryf&lt;br&gt;&lt;br&gt;Dwysedd isel (ysgafn)&lt;br&gt;&lt;br&gt;Ddim yn pydru&lt;br&gt;&lt;br&gt;Gwrthgyrydol&lt;br&gt;&lt;br&gt;Hyblyg</t>
+  </si>
+  <si>
+    <t>Cynhyrchion hylosgiad tanwydd hydrogen?</t>
+  </si>
+  <si>
+    <t>Dŵr</t>
+  </si>
+  <si>
+    <t>Manteision defnyddio hydrogen fel tanwydd?</t>
+  </si>
+  <si>
+    <t>Adnewyddadwy (cael ei ffurfio o ddŵr)&lt;br&gt;&lt;br&gt;Mae'n tanio'n hawdd&lt;br&gt;&lt;br&gt;Dim ond y cynhyrchu dŵr wrth ei hylosgi</t>
+  </si>
+  <si>
+    <t>Anfanteision defnyddio hydrogen fel tanwydd?</t>
+  </si>
+  <si>
+    <t>Angen llawer o egni trydanol i gynhyrchu hydrogen (drud)&lt;br&gt;&lt;br&gt;Angen cynhwysydd mawr a trwm i'w storio&lt;br&gt;&lt;br&gt;Ffrwydrol</t>
+  </si>
+  <si>
+    <t>Beth yw'r 3 ffactor sydd ei angen i gynnau a chadw tân yn llosgi?</t>
+  </si>
+  <si>
+    <t>TANWYDD&lt;BR&gt;&lt;BR&gt;OCSIGEN&lt;BR&gt;&lt;BR&gt;GWRES</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1024,6 +1195,18 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1052,7 +1235,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1087,6 +1270,10 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1102,10 +1289,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2629,11 +2812,14 @@
       </c>
     </row>
     <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>265</v>
+      </c>
       <c r="B22" t="s">
-        <v>284</v>
+        <v>266</v>
       </c>
       <c r="C22" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="33" customFormat="1"/>
@@ -2669,89 +2855,89 @@
     </row>
     <row r="2" spans="1:6" ht="27.75" customHeight="1">
       <c r="A2" s="14" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="27.75" customHeight="1">
       <c r="A3" s="14" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="27.75" customHeight="1">
       <c r="A4" s="14" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1">
       <c r="A5" s="14" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="27.75" customHeight="1">
       <c r="A6" s="14" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="27.75" customHeight="1">
       <c r="A7" s="14" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="27.75" customHeight="1">
       <c r="A8" s="15" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="27.75" customHeight="1">
       <c r="A9" s="15" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B9" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="C9" s="14" t="s">
         <v>281</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="27.75" customHeight="1">
       <c r="A10" s="15" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="27.75" customHeight="1"/>
@@ -2782,10 +2968,16 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1D33F75-CDBA-43E0-9D68-0D698FDC504D}">
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <dimension ref="A1:D56"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="68.140625" style="18" customWidth="1"/>
+    <col min="2" max="2" width="52.140625" style="18" customWidth="1"/>
+    <col min="3" max="4" width="42.140625" style="18" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="18"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="47.25">
+    <row r="1" spans="1:4" ht="31.5" customHeight="1">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -2799,6 +2991,278 @@
         <v>3</v>
       </c>
     </row>
+    <row r="2" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A2" s="18" t="s">
+        <v>286</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A3" s="18" t="s">
+        <v>288</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A4" s="18" t="s">
+        <v>290</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A5" s="18" t="s">
+        <v>292</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A6" s="18" t="s">
+        <v>294</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A7" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A8" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A9" s="18" t="s">
+        <v>300</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A10" s="18" t="s">
+        <v>301</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A11" s="18" t="s">
+        <v>303</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A12" s="18" t="s">
+        <v>305</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A13" s="18" t="s">
+        <v>307</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A14" s="18" t="s">
+        <v>309</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A15" s="18" t="s">
+        <v>310</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A16" s="18" t="s">
+        <v>311</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="31.5" customHeight="1">
+      <c r="A17" s="18" t="s">
+        <v>312</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="31.5" customHeight="1">
+      <c r="A18" s="18" t="s">
+        <v>313</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="31.5" customHeight="1">
+      <c r="A19" s="18" t="s">
+        <v>314</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="31.5" customHeight="1">
+      <c r="A20" s="18" t="s">
+        <v>316</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="31.5" customHeight="1">
+      <c r="A21" s="18" t="s">
+        <v>318</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="31.5" customHeight="1">
+      <c r="A22" s="18" t="s">
+        <v>320</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="31.5" customHeight="1">
+      <c r="A23" s="18" t="s">
+        <v>322</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="31.5" customHeight="1">
+      <c r="A24" s="18" t="s">
+        <v>324</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="31.5" customHeight="1">
+      <c r="A25" s="18" t="s">
+        <v>326</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="31.5" customHeight="1">
+      <c r="A26" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="31.5" customHeight="1">
+      <c r="A27" s="18" t="s">
+        <v>330</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="31.5" customHeight="1">
+      <c r="A28" s="18" t="s">
+        <v>332</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="31.5" customHeight="1">
+      <c r="A29" s="18" t="s">
+        <v>334</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="31.5" customHeight="1">
+      <c r="A30" s="18" t="s">
+        <v>336</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="31.5" customHeight="1">
+      <c r="A31" s="18" t="s">
+        <v>338</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="31.5" customHeight="1">
+      <c r="A32" s="18" t="s">
+        <v>340</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="33" s="18" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="34" s="18" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="35" s="18" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="36" s="18" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="37" s="18" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="38" s="18" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="39" s="18" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="40" s="18" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="41" s="18" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="42" s="18" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="43" s="18" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="44" s="18" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="45" s="18" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="46" s="18" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="47" s="18" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="48" s="18" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="49" s="18" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="50" s="18" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="51" s="18" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="52" s="18" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="53" s="18" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="54" s="18" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="55" s="18" customFormat="1" ht="31.5" customHeight="1"/>
+    <row r="56" s="18" customFormat="1" ht="31.5" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
